--- a/data/words.xlsx
+++ b/data/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14544\Desktop\TOEIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0844D94-1DAA-4117-944B-884044AD0E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151E673F-980C-4A2F-A0E3-E019EFD402C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17052" yWindow="0" windowWidth="6084" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="听力语法单词" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="2079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2932" uniqueCount="2487">
   <si>
     <t>单词</t>
     <phoneticPr fontId="1"/>
@@ -35524,6 +35524,1283 @@
   <si>
     <t>相关词</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>manufacturing</t>
+  </si>
+  <si>
+    <t>committee</t>
+  </si>
+  <si>
+    <t>in time</t>
+  </si>
+  <si>
+    <t>termination</t>
+  </si>
+  <si>
+    <t>rose</t>
+  </si>
+  <si>
+    <t>drop in</t>
+  </si>
+  <si>
+    <t>struggling</t>
+  </si>
+  <si>
+    <t>struggle</t>
+  </si>
+  <si>
+    <t>deflation</t>
+  </si>
+  <si>
+    <t>grip</t>
+  </si>
+  <si>
+    <t>apply</t>
+  </si>
+  <si>
+    <t>arranged for</t>
+  </si>
+  <si>
+    <t>report on</t>
+  </si>
+  <si>
+    <t>assign</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>efficiency</t>
+  </si>
+  <si>
+    <t>/ɪˈfɪʃənsi/</t>
+  </si>
+  <si>
+    <t>效率；效能（做事快且耗费少）</t>
+  </si>
+  <si>
+    <t>We need to improve efficiency.
+A: Any bottlenecks? B: Yes—efficiency is low in this step.</t>
+  </si>
+  <si>
+    <t>improve efficiency; efficiency gains; energy efficiency; operational efficiency</t>
+  </si>
+  <si>
+    <t>efficient（有效率的）+ -cy（名词后缀：性质/状态）</t>
+  </si>
+  <si>
+    <t>plural efficiencies</t>
+  </si>
+  <si>
+    <t>efficient（有效率的）；efficiently（高效地）；productivity（生产率）</t>
+  </si>
+  <si>
+    <t>/ɪˈfɪʃənt/</t>
+  </si>
+  <si>
+    <t>This machine is very efficient.
+A: Can we reduce costs? B: Use a more efficient process.</t>
+  </si>
+  <si>
+    <t>efficient at; efficient in; energy-efficient; highly efficient</t>
+  </si>
+  <si>
+    <t>effic-（起作用）+ -ient（形容词后缀：…的/倾向于…）</t>
+  </si>
+  <si>
+    <t>comparative more efficient; superlative most efficient</t>
+  </si>
+  <si>
+    <t>efficiency（效率）；efficiently（高效地）；inefficient（低效的）</t>
+  </si>
+  <si>
+    <t>efficiently</t>
+  </si>
+  <si>
+    <t>/ɪˈfɪʃəntli/</t>
+  </si>
+  <si>
+    <t>高效地；有效率地</t>
+  </si>
+  <si>
+    <t>The team worked efficiently.
+A: Why so fast? B: We planned efficiently.</t>
+  </si>
+  <si>
+    <t>work efficiently; operate efficiently; run efficiently</t>
+  </si>
+  <si>
+    <t>efficient + -ly（副词后缀）</t>
+  </si>
+  <si>
+    <t>efficient（高效的）；efficiency（效率）</t>
+  </si>
+  <si>
+    <t>efficacy</t>
+  </si>
+  <si>
+    <t>/ˈefɪkəsi/</t>
+  </si>
+  <si>
+    <t>功效；效力（尤指药效/措施效果，正式语域）</t>
+  </si>
+  <si>
+    <t>The study measured the efficacy of the drug.
+A: Does it work? B: Clinical efficacy looks strong.</t>
+  </si>
+  <si>
+    <t>efficacy of; demonstrate efficacy; clinical efficacy; proven efficacy</t>
+  </si>
+  <si>
+    <t>effic-（有效）+ -acy（名词后缀：性质/状态）</t>
+  </si>
+  <si>
+    <t>plural efficacies（较少）</t>
+  </si>
+  <si>
+    <t>effective（有效的）；effectiveness（有效性）；efficiency（效率，概念不同）</t>
+  </si>
+  <si>
+    <t>/ɪnˈspekt/</t>
+  </si>
+  <si>
+    <t>Inspect the equipment before use.
+A: Is it safe? B: It has been inspected.</t>
+  </si>
+  <si>
+    <t>inspect for; inspect a site/building; inspect closely</t>
+  </si>
+  <si>
+    <t>3rd inspects; past inspected; pp inspected; ing inspecting</t>
+  </si>
+  <si>
+    <t>inspection（检查）；inspector（检查员）</t>
+  </si>
+  <si>
+    <t>up to</t>
+  </si>
+  <si>
+    <t>phrase (prep./idiom)</t>
+  </si>
+  <si>
+    <t>/ˈʌp tuː/</t>
+  </si>
+  <si>
+    <t>最多到；直到；由…决定；在忙于（做…）</t>
+  </si>
+  <si>
+    <t>You can take up to two bags.
+A: Who decides? B: It’s up to you.</t>
+  </si>
+  <si>
+    <t>up to + number; up to now; up to date; be up to someone; be up to something</t>
+  </si>
+  <si>
+    <t>固定短语：up（至/向上）+ to（到）</t>
+  </si>
+  <si>
+    <t>up-to-date（最新的）；up to speed（熟悉情况）</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>/ˈveəriəbl/</t>
+  </si>
+  <si>
+    <t>/ˈveriəbl/</t>
+  </si>
+  <si>
+    <t>n. 变量；可变因素；adj. 可变的；多变的</t>
+  </si>
+  <si>
+    <t>In statistics, a variable can be continuous.
+A: Why inconsistent? B: The results are variable.</t>
+  </si>
+  <si>
+    <t>independent/dependent variable; variable costs; highly variable; variable rate</t>
+  </si>
+  <si>
+    <t>vary（变化）+ -able（形容词后缀：可…的）</t>
+  </si>
+  <si>
+    <t>n. plural variables; adj. comparative more variable; superlative most variable</t>
+  </si>
+  <si>
+    <t>vary（变化）；various（各种各样的）；variability（变异性）</t>
+  </si>
+  <si>
+    <t>various</t>
+  </si>
+  <si>
+    <t>/ˈveəriəs/</t>
+  </si>
+  <si>
+    <t>/ˈveriəs/</t>
+  </si>
+  <si>
+    <t>各种各样的；多种的</t>
+  </si>
+  <si>
+    <t>We discussed various options.
+A: Any reasons? B: For various reasons.</t>
+  </si>
+  <si>
+    <t>various kinds of; various reasons; at various times</t>
+  </si>
+  <si>
+    <t>vary + -ous（形容词后缀：充满…的）</t>
+  </si>
+  <si>
+    <t>vary（变化）；variety（多样性）；variable（变量/可变的）</t>
+  </si>
+  <si>
+    <t>vary</t>
+  </si>
+  <si>
+    <t>/ˈveəri/</t>
+  </si>
+  <si>
+    <t>/ˈveri/</t>
+  </si>
+  <si>
+    <t>变化；不同；使变化</t>
+  </si>
+  <si>
+    <t>Prices vary by region.
+A: Same for everyone? B: No, it varies.</t>
+  </si>
+  <si>
+    <t>vary from...to...; vary by; vary with; vary widely</t>
+  </si>
+  <si>
+    <t>词根 var（变化）</t>
+  </si>
+  <si>
+    <t>3rd varies; past varied; pp varied; ing varying</t>
+  </si>
+  <si>
+    <t>variety（多样性）；various（多种的）；variation（变化）</t>
+  </si>
+  <si>
+    <t>variety</t>
+  </si>
+  <si>
+    <t>/vəˈraɪəti/</t>
+  </si>
+  <si>
+    <t>多样性；种类；品种</t>
+  </si>
+  <si>
+    <t>The store offers a wide variety of products.
+A: Bored? B: Try it for variety.</t>
+  </si>
+  <si>
+    <t>a variety of; wide variety; variety show; for variety</t>
+  </si>
+  <si>
+    <t>vary + -ety（名词后缀：性质/状态）</t>
+  </si>
+  <si>
+    <t>plural varieties</t>
+  </si>
+  <si>
+    <t>various（各种的）；variation（变化）；diversity（多样性）</t>
+  </si>
+  <si>
+    <t>comprehensive</t>
+  </si>
+  <si>
+    <t>/ˌkɒmprɪˈhensɪv/</t>
+  </si>
+  <si>
+    <t>/ˌkɑːmprɪˈhensɪv/</t>
+  </si>
+  <si>
+    <t>全面的；综合的</t>
+  </si>
+  <si>
+    <t>We need a comprehensive plan.
+A: Quick summary? B: I’ll provide a comprehensive review.</t>
+  </si>
+  <si>
+    <t>comprehensive plan; comprehensive analysis; comprehensive coverage</t>
+  </si>
+  <si>
+    <t>comprehend（理解）+ -ive（形容词后缀）</t>
+  </si>
+  <si>
+    <t>comparative more comprehensive; superlative most comprehensive</t>
+  </si>
+  <si>
+    <t>comprehend（理解）；comprehension（理解力）；comprehensiveness（全面性）</t>
+  </si>
+  <si>
+    <t>comprehensiveness</t>
+  </si>
+  <si>
+    <t>/ˌkɒmprɪˈhensɪvnəs/</t>
+  </si>
+  <si>
+    <t>/ˌkɑːmprɪˈhensɪvnəs/</t>
+  </si>
+  <si>
+    <t>全面性；综合性</t>
+  </si>
+  <si>
+    <t>The report’s comprehensiveness impressed the client.
+A: Anything missing? B: No—the comprehensiveness is high.</t>
+  </si>
+  <si>
+    <t>comprehensiveness of; ensure comprehensiveness; comprehensiveness and accuracy</t>
+  </si>
+  <si>
+    <t>comprehensive + -ness（名词后缀：性质/状态）</t>
+  </si>
+  <si>
+    <t>—（一般不可数）</t>
+  </si>
+  <si>
+    <t>comprehensive（全面的）；comprehensively（全面地）</t>
+  </si>
+  <si>
+    <t>comprehend</t>
+  </si>
+  <si>
+    <t>/ˌkɒmprɪˈhend/</t>
+  </si>
+  <si>
+    <t>/ˌkɑːmprɪˈhend/</t>
+  </si>
+  <si>
+    <t>理解；领会（较正式）</t>
+  </si>
+  <si>
+    <t>I can’t comprehend why he left.
+A: Do you understand? B: I comprehend the main idea.</t>
+  </si>
+  <si>
+    <t>comprehend why/how; comprehend the meaning; fully comprehend</t>
+  </si>
+  <si>
+    <t>com-（完全）+ prehend（抓住）</t>
+  </si>
+  <si>
+    <t>3rd comprehends; past comprehended; pp comprehended; ing comprehending</t>
+  </si>
+  <si>
+    <t>comprehension（理解）；comprehensible（可理解的）；incomprehensible（难懂的）</t>
+  </si>
+  <si>
+    <t>comprehension</t>
+  </si>
+  <si>
+    <t>/ˌkɒmprɪˈhenʃən/</t>
+  </si>
+  <si>
+    <t>/ˌkɑːmprɪˈhenʃən/</t>
+  </si>
+  <si>
+    <t>理解；理解力；（考试）阅读理解</t>
+  </si>
+  <si>
+    <t>Listening comprehension takes practice.
+A: How is his comprehension? B: Very good.</t>
+  </si>
+  <si>
+    <t>reading/listening comprehension; comprehension of; comprehension skills</t>
+  </si>
+  <si>
+    <t>comprehend + -sion（名词后缀）</t>
+  </si>
+  <si>
+    <t>plural comprehensions（少用）</t>
+  </si>
+  <si>
+    <t>comprehend（理解）；comprehensible（可理解的）；comprehensive（全面的）</t>
+  </si>
+  <si>
+    <t>standpoint</t>
+  </si>
+  <si>
+    <t>/ˈstændpɔɪnt/</t>
+  </si>
+  <si>
+    <t>立场；观点</t>
+  </si>
+  <si>
+    <t>From a legal standpoint, it’s risky.
+A: Your view? B: From my standpoint, it’s fair.</t>
+  </si>
+  <si>
+    <t>from a standpoint; from the standpoint of; moral/legal standpoint</t>
+  </si>
+  <si>
+    <t>stand + point（复合名词）</t>
+  </si>
+  <si>
+    <t>plural standpoints</t>
+  </si>
+  <si>
+    <t>perspective（视角）；viewpoint（观点）；position（立场）</t>
+  </si>
+  <si>
+    <t>successive</t>
+  </si>
+  <si>
+    <t>/səkˈsesɪv/</t>
+  </si>
+  <si>
+    <t>连续的；接连的（逐个发生）</t>
+  </si>
+  <si>
+    <t>He won three successive titles.
+A: Again? B: Yes—successive failures.</t>
+  </si>
+  <si>
+    <t>successive days/years; successive steps; in successive order</t>
+  </si>
+  <si>
+    <t>success + -ive（形容词后缀）</t>
+  </si>
+  <si>
+    <t>comparative more successive; superlative most successive（少用）</t>
+  </si>
+  <si>
+    <t>succession（连续/继任）；successor（继任者）</t>
+  </si>
+  <si>
+    <t>succession</t>
+  </si>
+  <si>
+    <t>/səkˈseʃən/</t>
+  </si>
+  <si>
+    <t>连续；一连串；继任；继承</t>
+  </si>
+  <si>
+    <t>A succession of storms hit the coast.
+A: Who’s next? B: There’s a succession plan.</t>
+  </si>
+  <si>
+    <t>a succession of; in quick succession; line of succession; succession plan</t>
+  </si>
+  <si>
+    <t>succeed + -sion（名词后缀）</t>
+  </si>
+  <si>
+    <t>plural successions</t>
+  </si>
+  <si>
+    <t>successive（连续的）；successor（继任者）；succession planning（继任规划）</t>
+  </si>
+  <si>
+    <t>considerable</t>
+  </si>
+  <si>
+    <t>/kənˈsɪdərəbl/</t>
+  </si>
+  <si>
+    <t>相当大的；可观的</t>
+  </si>
+  <si>
+    <t>It took a considerable amount of time.
+A: Big cost? B: Yes, a considerable expense.</t>
+  </si>
+  <si>
+    <t>considerable amount/time; considerable interest; a considerable number of</t>
+  </si>
+  <si>
+    <t>consider + -able（形容词后缀）</t>
+  </si>
+  <si>
+    <t>comparative more considerable; superlative most considerable</t>
+  </si>
+  <si>
+    <t>considerably（相当地）；consideration（考虑）</t>
+  </si>
+  <si>
+    <t>considerate</t>
+  </si>
+  <si>
+    <t>/kənˈsɪdərət/</t>
+  </si>
+  <si>
+    <t>体贴的；考虑周到的</t>
+  </si>
+  <si>
+    <t>That was very considerate of you.
+A: Late-night noise? B: Be considerate of neighbors.</t>
+  </si>
+  <si>
+    <t>considerate of; considerate towards; be considerate</t>
+  </si>
+  <si>
+    <t>consider + -ate（形容词化后缀）</t>
+  </si>
+  <si>
+    <t>comparative more considerate; superlative most considerate</t>
+  </si>
+  <si>
+    <t>consideration（体谅/考虑）；considerately（体贴地）</t>
+  </si>
+  <si>
+    <t>consideration</t>
+  </si>
+  <si>
+    <t>/kənˌsɪdəˈreɪʃən/</t>
+  </si>
+  <si>
+    <t>考虑；体谅；（法律）对价</t>
+  </si>
+  <si>
+    <t>Thank you for your consideration.
+A: Decision? B: After careful consideration.</t>
+  </si>
+  <si>
+    <t>take into consideration; under consideration; for your consideration; subject to consideration</t>
+  </si>
+  <si>
+    <t>consider + -ation（名词后缀）</t>
+  </si>
+  <si>
+    <t>plural considerations</t>
+  </si>
+  <si>
+    <t>consider（考虑）；considerate（体贴的）；considerable（可观的）</t>
+  </si>
+  <si>
+    <t>consider</t>
+  </si>
+  <si>
+    <t>/kənˈsɪdə/</t>
+  </si>
+  <si>
+    <t>/kənˈsɪdər/</t>
+  </si>
+  <si>
+    <t>考虑；认为；把…看作</t>
+  </si>
+  <si>
+    <t>Please consider my application.
+A: Priority? B: We consider it urgent.</t>
+  </si>
+  <si>
+    <t>consider doing; consider + wh-; consider it + adj/n; consider as</t>
+  </si>
+  <si>
+    <t>con-（共同）+ sider（看）</t>
+  </si>
+  <si>
+    <t>3rd considers; past considered; pp considered; ing considering</t>
+  </si>
+  <si>
+    <t>consideration（考虑）；considerate（体贴的）；considerable（可观的）</t>
+  </si>
+  <si>
+    <t>timed</t>
+  </si>
+  <si>
+    <t>/taɪmd/</t>
+  </si>
+  <si>
+    <t>定时的；计时的；（pp）time 的过去分词</t>
+  </si>
+  <si>
+    <t>This is a timed test.
+A: Why the clock? B: It’s timed.</t>
+  </si>
+  <si>
+    <t>timed test; timed entry; timed event; well-timed</t>
+  </si>
+  <si>
+    <t>time + -ed（过去分词/形容词化）</t>
+  </si>
+  <si>
+    <t>time: 3rd times; past timed; pp timed; ing timing</t>
+  </si>
+  <si>
+    <t>timely（及时的）；timing（时机/计时）</t>
+  </si>
+  <si>
+    <t>timely</t>
+  </si>
+  <si>
+    <t>/ˈtaɪmli/</t>
+  </si>
+  <si>
+    <t>及时的；适时的</t>
+  </si>
+  <si>
+    <t>A timely warning prevented an accident.
+A: Helpful? B: Yes, a timely reminder.</t>
+  </si>
+  <si>
+    <t>timely manner; timely response; timely warning</t>
+  </si>
+  <si>
+    <t>time + -ly（形容词后缀：…的；此处非副词）</t>
+  </si>
+  <si>
+    <t>comparative more timely; superlative most timely</t>
+  </si>
+  <si>
+    <t>timeliness（及时性）；in time（及时/最终）</t>
+  </si>
+  <si>
+    <t>roster</t>
+  </si>
+  <si>
+    <t>/ˈrɒstə/</t>
+  </si>
+  <si>
+    <t>/ˈrɑːstər/</t>
+  </si>
+  <si>
+    <t>n. 名单；值班表；花名册；v. 排班/列入名单</t>
+  </si>
+  <si>
+    <t>The roster is posted on the wall.
+A: Who’s on duty? B: Check the roster.</t>
+  </si>
+  <si>
+    <t>on the roster; duty roster; staff roster; roster someone for</t>
+  </si>
+  <si>
+    <t>词缀不典型；职场/体育语域常用</t>
+  </si>
+  <si>
+    <t>n. plural rosters; v. 3rd rosters / past rostered / pp rostered / ing rostering</t>
+  </si>
+  <si>
+    <t>schedule（排班表）；list（名单）；line-up（阵容）</t>
+  </si>
+  <si>
+    <t>appropriately</t>
+  </si>
+  <si>
+    <t>/əˈprəʊpriətli/</t>
+  </si>
+  <si>
+    <t>/əˈproʊpriətli/</t>
+  </si>
+  <si>
+    <t>适当地；得体地</t>
+  </si>
+  <si>
+    <t>Please dress appropriately.
+A: Is this okay? B: Yes, appropriately formal.</t>
+  </si>
+  <si>
+    <t>appropriately dressed; respond appropriately; behave appropriately</t>
+  </si>
+  <si>
+    <t>appropriate + -ly（副词后缀）</t>
+  </si>
+  <si>
+    <t>appropriate（合适的）；appropriateness（得体/适当性）</t>
+  </si>
+  <si>
+    <t>/ˌmænjuˈfæktʃərɪŋ/</t>
+  </si>
+  <si>
+    <t>制造业；制造；（adj.）制造的；生产的</t>
+  </si>
+  <si>
+    <t>Manufacturing is a major sector.
+A: Which team? B: Manufacturing.</t>
+  </si>
+  <si>
+    <t>manufacturing process; manufacturing plant; manufacturing sector</t>
+  </si>
+  <si>
+    <t>manufacture（制造）+ -ing（动名词/形容词化）</t>
+  </si>
+  <si>
+    <t>—（多作不可数名词；也可作形容词）</t>
+  </si>
+  <si>
+    <t>manufacture（制造）；manufacturer（制造商）；manufactured（加工制造的）</t>
+  </si>
+  <si>
+    <t>equip</t>
+  </si>
+  <si>
+    <t>/ɪˈkwɪp/</t>
+  </si>
+  <si>
+    <t>装备；配备；使具备（能力/知识）</t>
+  </si>
+  <si>
+    <t>The lab is equipped with modern tools.
+A: Ready? B: Training will equip you.</t>
+  </si>
+  <si>
+    <t>equip with; equip someone to do; well-equipped</t>
+  </si>
+  <si>
+    <t>equ-（同等）+ -ip（装备语源）</t>
+  </si>
+  <si>
+    <t>3rd equips; past equipped; pp equipped; ing equipping</t>
+  </si>
+  <si>
+    <t>equipment（设备）；equipped（配备齐全的）</t>
+  </si>
+  <si>
+    <t>n. (uncount.)</t>
+  </si>
+  <si>
+    <t>/ɪˈkwɪpmənt/</t>
+  </si>
+  <si>
+    <t>设备；器材（不可数）</t>
+  </si>
+  <si>
+    <t>Safety equipment is required.
+A: Need tools? B: The equipment is here.</t>
+  </si>
+  <si>
+    <t>office equipment; safety equipment; a piece of equipment</t>
+  </si>
+  <si>
+    <t>equip + -ment（名词后缀）</t>
+  </si>
+  <si>
+    <t>不可数；数量表达：a piece of equipment / two pieces of equipment</t>
+  </si>
+  <si>
+    <t>equip（配备）；gear（装备，口语）</t>
+  </si>
+  <si>
+    <t>equipped</t>
+  </si>
+  <si>
+    <t>/ɪˈkwɪpt/</t>
+  </si>
+  <si>
+    <t>装备齐全的；具备…能力的；（pp）equip 的过去分词</t>
+  </si>
+  <si>
+    <t>The room is equipped with a projector.
+A: Can she do it? B: She’s well equipped.</t>
+  </si>
+  <si>
+    <t>equipped with; well equipped; fully equipped; equipped for</t>
+  </si>
+  <si>
+    <t>equip + -ed（过去分词/形容词化）</t>
+  </si>
+  <si>
+    <t>equip: 3rd equips; past equipped; pp equipped; ing equipping</t>
+  </si>
+  <si>
+    <t>equipment（设备）；equip（配备）</t>
+  </si>
+  <si>
+    <t>/kəˈmɪti/</t>
+  </si>
+  <si>
+    <t>委员会</t>
+  </si>
+  <si>
+    <t>A committee reviewed the proposal.
+A: Who decides? B: The committee will vote.</t>
+  </si>
+  <si>
+    <t>committee meeting; committee member; on the committee; committee chair</t>
+  </si>
+  <si>
+    <t>commit + -ee（名词后缀：人/机构）</t>
+  </si>
+  <si>
+    <t>plural committees</t>
+  </si>
+  <si>
+    <t>commission（委员会/委任）；board（董事会）；subcommittee（小组委员会）</t>
+  </si>
+  <si>
+    <t>phrase (adv./idiom)</t>
+  </si>
+  <si>
+    <t>/ɪn ˈtaɪm/</t>
+  </si>
+  <si>
+    <t>及时；最终（过一段时间后）</t>
+  </si>
+  <si>
+    <t>We arrived just in time.
+A: Will it improve? B: Yes, in time.</t>
+  </si>
+  <si>
+    <t>in time for; just in time; in time to do; on time（对比）</t>
+  </si>
+  <si>
+    <t>固定短语：in + time</t>
+  </si>
+  <si>
+    <t>on time（准时）；timely（及时的）；timing（时机）</t>
+  </si>
+  <si>
+    <t>clerk</t>
+  </si>
+  <si>
+    <t>/klɑːk/</t>
+  </si>
+  <si>
+    <t>/klɝːk/</t>
+  </si>
+  <si>
+    <t>店员；职员；文员；书记员</t>
+  </si>
+  <si>
+    <t>The clerk helped me fill out the form.
+A: Where do I pay? B: Ask the clerk at the counter.</t>
+  </si>
+  <si>
+    <t>store/shop clerk; desk clerk; clerk of court; clerk at/in</t>
+  </si>
+  <si>
+    <t>职业名词；词缀不典型</t>
+  </si>
+  <si>
+    <t>plural clerks</t>
+  </si>
+  <si>
+    <t>receptionist（前台）；cashier（收银员）；assistant（助理/店员）</t>
+  </si>
+  <si>
+    <t>lightly</t>
+  </si>
+  <si>
+    <t>/ˈlaɪtli/</t>
+  </si>
+  <si>
+    <t>轻轻地；轻微地；不严肃地</t>
+  </si>
+  <si>
+    <t>Knock lightly before entering.
+A: Serious? B: Don’t take it lightly.</t>
+  </si>
+  <si>
+    <t>touch lightly; lightly fried; take something lightly; tread lightly</t>
+  </si>
+  <si>
+    <t>light + -ly（副词后缀）</t>
+  </si>
+  <si>
+    <t>light（轻的/光）；lighten（减轻）；lightweight（轻量的）</t>
+  </si>
+  <si>
+    <t>lighting</t>
+  </si>
+  <si>
+    <t>/ˈlaɪtɪŋ/</t>
+  </si>
+  <si>
+    <t>照明；灯光（系统/整体）</t>
+  </si>
+  <si>
+    <t>The lighting in this room is excellent.
+A: Too dark? B: We need better lighting.</t>
+  </si>
+  <si>
+    <t>lighting design; lighting system; ambient lighting; stage lighting</t>
+  </si>
+  <si>
+    <t>light + -ing（动名词名词化）</t>
+  </si>
+  <si>
+    <t>light（灯/光）；illuminate（照亮）；fixture（灯具）</t>
+  </si>
+  <si>
+    <t>lighted</t>
+  </si>
+  <si>
+    <t>adj./v.(past/pp)</t>
+  </si>
+  <si>
+    <t>/ˈlaɪtɪd/</t>
+  </si>
+  <si>
+    <t>点亮的；（v）light 的过去式/过去分词（lighted；lit 也常用）</t>
+  </si>
+  <si>
+    <t>A lighted sign guided us.
+A: Did you light the candle? B: Yes, I lighted it. (also: I lit it.)</t>
+  </si>
+  <si>
+    <t>lighted sign/candle; light a candle; lighted path</t>
+  </si>
+  <si>
+    <t>light + -ed（过去分词/形容词化）</t>
+  </si>
+  <si>
+    <t>light: 3rd lights; past lit/lighted; pp lit/lighted; ing lighting</t>
+  </si>
+  <si>
+    <t>lit（点亮的/过去式）；unlit（未点燃的）；light（点燃/照亮）</t>
+  </si>
+  <si>
+    <t>/ˌtɜːmɪˈneɪʃən/</t>
+  </si>
+  <si>
+    <t>/ˌtɝːmɪˈneɪʃən/</t>
+  </si>
+  <si>
+    <t>终止；结束；解雇（合同/雇佣关系）；（电）端接</t>
+  </si>
+  <si>
+    <t>The contract allows early termination.
+A: Why did he leave? B: His termination was unexpected.</t>
+  </si>
+  <si>
+    <t>termination of; contract termination; employment termination; termination notice; termination fee</t>
+  </si>
+  <si>
+    <t>terminate（终止）+ -ion（名词后缀：过程/结果；常用于名词）</t>
+  </si>
+  <si>
+    <t>plural terminations</t>
+  </si>
+  <si>
+    <t>terminate（终止）；terminated（被终止的）；terminal（末端的/终端）</t>
+  </si>
+  <si>
+    <t>n./v.(past)</t>
+  </si>
+  <si>
+    <t>/rəʊz/</t>
+  </si>
+  <si>
+    <t>/roʊz/</t>
+  </si>
+  <si>
+    <t>n. 玫瑰；v. rise 的过去式：上升；起身；兴起</t>
+  </si>
+  <si>
+    <t>Prices rose sharply last month.
+A: Did he stand up? B: Yes, he rose.</t>
+  </si>
+  <si>
+    <t>rose to; rose from; rose sharply/steadily; a rose garden</t>
+  </si>
+  <si>
+    <t>rose（名词：花）与 rise→rose（动词过去式）同形</t>
+  </si>
+  <si>
+    <t>rise: 3rd rises; past rose; pp risen; ing rising
+rose(n.): plural roses</t>
+  </si>
+  <si>
+    <t>rise（上升）；risen（上升的/过去分词）；rising（上升的）</t>
+  </si>
+  <si>
+    <t>/ˈprɒfɪtəbl/</t>
+  </si>
+  <si>
+    <t>/ˈprɑːfɪtəbl/</t>
+  </si>
+  <si>
+    <t>盈利的；有利可图的；有益的</t>
+  </si>
+  <si>
+    <t>The business became profitable within a year.
+A: Worth doing? B: It could be profitable.</t>
+  </si>
+  <si>
+    <t>profitable business; highly profitable; profitable to do; profitable for</t>
+  </si>
+  <si>
+    <t>profit（利润）+ -able（形容词后缀：可…的）</t>
+  </si>
+  <si>
+    <t>comparative more profitable; superlative most profitable</t>
+  </si>
+  <si>
+    <t>profit（利润）；profitability（盈利能力）；unprofitable（不盈利的）</t>
+  </si>
+  <si>
+    <t>phrasal v./n.</t>
+  </si>
+  <si>
+    <t>/ˌdrɒp ˈɪn/</t>
+  </si>
+  <si>
+    <t>/ˌdrɑːp ˈɪn/</t>
+  </si>
+  <si>
+    <t>v. 顺道拜访；突然来访；（数量）下降一点；n. 小幅下降</t>
+  </si>
+  <si>
+    <t>Feel free to drop in any time.
+A: Sales? B: There was a drop in demand.</t>
+  </si>
+  <si>
+    <t>drop in on; drop in to; drop in by; a drop in prices; a drop in attendance</t>
+  </si>
+  <si>
+    <t>drop（落下/下降）+ in（进入）构成短语动词</t>
+  </si>
+  <si>
+    <t>drop: 3rd drops; past dropped; pp dropped; ing dropping</t>
+  </si>
+  <si>
+    <t>drop by（顺道）；drop off（下降/送到）；increase（上升）</t>
+  </si>
+  <si>
+    <t>adj./v.(ing)</t>
+  </si>
+  <si>
+    <t>/ˈstrʌɡlɪŋ/</t>
+  </si>
+  <si>
+    <t>adj. 苦苦挣扎的；艰难维持的；v. struggle 的现在分词</t>
+  </si>
+  <si>
+    <t>Many small firms are struggling.
+A: Deadline? B: We’re struggling to meet it.</t>
+  </si>
+  <si>
+    <t>struggling with; struggling to do; struggling business; struggling economy</t>
+  </si>
+  <si>
+    <t>struggle + -ing（现在分词/形容词化）</t>
+  </si>
+  <si>
+    <t>struggle: 3rd struggles; past struggled; pp struggled; ing struggling</t>
+  </si>
+  <si>
+    <t>struggle（奋斗/挣扎）；struggler（奋斗者）；struggle for（为…奋斗）</t>
+  </si>
+  <si>
+    <t>/ˈstrʌɡl/</t>
+  </si>
+  <si>
+    <t>v. 奋斗；挣扎；努力；n. 斗争；挣扎</t>
+  </si>
+  <si>
+    <t>He struggled to stay awake.
+A: Is it easy? B: No, it’s a struggle.</t>
+  </si>
+  <si>
+    <t>struggle to do; struggle with; struggle against; power struggle</t>
+  </si>
+  <si>
+    <t>词缀不典型；常用核心词</t>
+  </si>
+  <si>
+    <t>v. 3rd struggles; past struggled; pp struggled; ing struggling
+n. plural struggles</t>
+  </si>
+  <si>
+    <t>struggling（艰难的）；hardship（困难）；effort（努力）</t>
+  </si>
+  <si>
+    <t>/dɪˈfleɪʃən/</t>
+  </si>
+  <si>
+    <t>通货紧缩；（经济）物价下降；（气）放气</t>
+  </si>
+  <si>
+    <t>The country slipped into deflation.
+A: Prices falling? B: Deflation is a risk.</t>
+  </si>
+  <si>
+    <t>deflationary pressure; deflation risk; in deflation; avoid deflation</t>
+  </si>
+  <si>
+    <t>de-（向下/去除）+ -flation（与 inflate 同源）+ -ion（名词后缀）</t>
+  </si>
+  <si>
+    <t>—（通常不可数）</t>
+  </si>
+  <si>
+    <t>inflation（通胀）；deflationary（通缩的）；disinflation（通胀回落）</t>
+  </si>
+  <si>
+    <t>/ɡrɪp/</t>
+  </si>
+  <si>
+    <t>n. 握；把手；控制；紧张感；v. 抓牢；牢牢影响/吸引</t>
+  </si>
+  <si>
+    <t>Hold the rail with a firm grip.
+A: Why frozen? B: Fear gripped me.</t>
+  </si>
+  <si>
+    <t>grip on; get/lose a grip; firm grip; grip someone’s attention</t>
+  </si>
+  <si>
+    <t>词缀不典型；多义核心词</t>
+  </si>
+  <si>
+    <t>n. plural grips; v. 3rd grips; past gripped; pp gripped; ing gripping</t>
+  </si>
+  <si>
+    <t>gripping（扣人心弦的）；handgrip（握把）；grip strength（握力）</t>
+  </si>
+  <si>
+    <t>/əˈplaɪ/</t>
+  </si>
+  <si>
+    <t>申请；应用；涂抹；适用</t>
+  </si>
+  <si>
+    <t>You can apply online.
+A: Does this rule apply to me? B: Yes, it applies to everyone.</t>
+  </si>
+  <si>
+    <t>apply for; apply to; apply sth to; apply pressure; apply for a job</t>
+  </si>
+  <si>
+    <t>ap-（向）+ ply（折叠/用力）语源；动词常用</t>
+  </si>
+  <si>
+    <t>3rd applies; past applied; pp applied; ing applying</t>
+  </si>
+  <si>
+    <t>application（申请/应用）；applicant（申请人）；applicable（适用的）</t>
+  </si>
+  <si>
+    <t>/əˈreɪndʒ/</t>
+  </si>
+  <si>
+    <t>安排；筹备；整理；布置</t>
+  </si>
+  <si>
+    <t>I’ll arrange a meeting for next week.
+A: Seats? B: We arranged them in a circle.</t>
+  </si>
+  <si>
+    <t>arrange for; arrange to do; arrange a meeting; arrange in/into; make arrangements</t>
+  </si>
+  <si>
+    <t>a-（加强）+ range（排列/范围语源相关）</t>
+  </si>
+  <si>
+    <t>3rd arranges; past arranged; pp arranged; ing arranging</t>
+  </si>
+  <si>
+    <t>arrangement（安排/布置）；arranged（安排好的）；rearrange（重新安排）</t>
+  </si>
+  <si>
+    <t>verb phrase</t>
+  </si>
+  <si>
+    <t>/əˈreɪndʒd fɔː/</t>
+  </si>
+  <si>
+    <t>/əˈreɪndʒd fɔːr/</t>
+  </si>
+  <si>
+    <t>安排好（某事发生/某人得到…）</t>
+  </si>
+  <si>
+    <t>I arranged for a taxi to pick you up.
+A: Hotel? B: I’ve arranged for a room.</t>
+  </si>
+  <si>
+    <t>arrange for someone to do; arrange for something to happen; arranged for + noun</t>
+  </si>
+  <si>
+    <t>arrange + for（介词搭配：为…安排）</t>
+  </si>
+  <si>
+    <t>arrange: 3rd arranges; past arranged; pp arranged; ing arranging</t>
+  </si>
+  <si>
+    <t>make arrangements（做安排）；arrangement（安排）</t>
+  </si>
+  <si>
+    <t>phrasal v.</t>
+  </si>
+  <si>
+    <t>/rɪˈpɔːt ɒn/</t>
+  </si>
+  <si>
+    <t>/rɪˈpɔːrt ɑːn/</t>
+  </si>
+  <si>
+    <t>就……报道/汇报</t>
+  </si>
+  <si>
+    <t>The journalist reported on the incident.
+A: Any updates? B: I’ll report on progress tomorrow.</t>
+  </si>
+  <si>
+    <t>report on progress; report on findings; report on an event; report back</t>
+  </si>
+  <si>
+    <t>report（报告/报道）+ on（关于）</t>
+  </si>
+  <si>
+    <t>report: 3rd reports; past reported; pp reported; ing reporting</t>
+  </si>
+  <si>
+    <t>report（报告）；reporter（记者）；reporting（报道/报告）</t>
+  </si>
+  <si>
+    <t>/əˈsaɪn/</t>
+  </si>
+  <si>
+    <t>分配；指派；布置（任务）</t>
+  </si>
+  <si>
+    <t>The manager assigned me a new task.
+A: Who handles it? B: I’ll assign someone.</t>
+  </si>
+  <si>
+    <t>assign to; assign a task; assign responsibility; assign someone to do</t>
+  </si>
+  <si>
+    <t>as-（向）+ sign（标记/签）→“指定”</t>
+  </si>
+  <si>
+    <t>3rd assigns; past assigned; pp assigned; ing assigning</t>
+  </si>
+  <si>
+    <t>assignment（任务/作业）；assignee（受让人）</t>
+  </si>
+  <si>
+    <t>/ˈdɪstrɪkt/</t>
+  </si>
+  <si>
+    <t>地区；行政区；（美）学区；选区</t>
+  </si>
+  <si>
+    <t>The school is in a quiet district.
+A: Which area? B: The business district downtown.</t>
+  </si>
+  <si>
+    <t>business district; school district; district court; electoral district</t>
+  </si>
+  <si>
+    <t>dis-（分开）+ strict（拉紧/束缚语源）→“划分区域”语源</t>
+  </si>
+  <si>
+    <t>plural districts</t>
+  </si>
+  <si>
+    <t>regional（地区的）；neighborhood（社区）；districting（划分选区）</t>
+  </si>
+  <si>
+    <t>He committed to the plan.
+A: Version control? B: I committed the changes.</t>
+  </si>
+  <si>
+    <t>She is committed to improving quality.
+A: Joining? B: Yes, I’m committed.</t>
+  </si>
+  <si>
+    <t>committed to; fully committed; committed member; be committed</t>
+  </si>
+  <si>
+    <t>commit + -ed（过去分词/形容词化）</t>
+  </si>
+  <si>
+    <t>commit（承诺）；commitment（承诺）；uncommitted（未承诺的）</t>
   </si>
 </sst>
 </file>
@@ -35875,7 +37152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J269"/>
+  <dimension ref="A1:K320"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.09765625" bestFit="1" customWidth="1"/>
@@ -42931,1570 +44208,3355 @@
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A221" s="5" t="s">
+      <c r="A221" t="s">
         <v>1694</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B221" t="s">
         <v>12</v>
       </c>
-      <c r="C221" s="5" t="s">
+      <c r="C221" t="s">
         <v>1734</v>
       </c>
-      <c r="D221" s="5" t="s">
+      <c r="D221" t="s">
         <v>1735</v>
       </c>
-      <c r="E221" s="5" t="s">
+      <c r="E221" t="s">
         <v>1736</v>
       </c>
-      <c r="F221" s="5" t="s">
+      <c r="F221" t="s">
         <v>1737</v>
       </c>
-      <c r="G221" s="5" t="s">
+      <c r="G221" t="s">
         <v>1738</v>
       </c>
-      <c r="H221" s="5" t="s">
+      <c r="H221" t="s">
         <v>1739</v>
       </c>
-      <c r="I221" s="5" t="s">
+      <c r="I221" t="s">
         <v>1740</v>
       </c>
-      <c r="J221" s="5">
+      <c r="J221">
         <v>8000</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A222" s="5" t="s">
+      <c r="A222" t="s">
         <v>1741</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="B222" t="s">
         <v>6</v>
       </c>
-      <c r="C222" s="5" t="s">
+      <c r="C222" t="s">
         <v>1742</v>
       </c>
-      <c r="D222" s="5" t="s">
+      <c r="D222" t="s">
         <v>1743</v>
       </c>
-      <c r="E222" s="5" t="s">
+      <c r="E222" t="s">
         <v>1744</v>
       </c>
-      <c r="F222" s="5" t="s">
+      <c r="F222" t="s">
         <v>1745</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" t="s">
         <v>1746</v>
       </c>
-      <c r="H222" s="5" t="s">
+      <c r="H222" t="s">
         <v>1747</v>
       </c>
-      <c r="I222" s="5" t="s">
+      <c r="I222" t="s">
         <v>1748</v>
       </c>
-      <c r="J222" s="5">
+      <c r="J222">
         <v>3000</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A223" s="5" t="s">
+      <c r="A223" t="s">
         <v>1695</v>
       </c>
-      <c r="B223" s="5" t="s">
+      <c r="B223" t="s">
         <v>15</v>
       </c>
-      <c r="C223" s="5" t="s">
+      <c r="C223" t="s">
         <v>1749</v>
       </c>
-      <c r="D223" s="5" t="s">
+      <c r="D223" t="s">
         <v>1750</v>
       </c>
-      <c r="E223" s="5" t="s">
+      <c r="E223" t="s">
         <v>1751</v>
       </c>
-      <c r="F223" s="5" t="s">
+      <c r="F223" t="s">
         <v>1752</v>
       </c>
-      <c r="G223" s="5" t="s">
+      <c r="G223" t="s">
         <v>1753</v>
       </c>
-      <c r="H223" s="5" t="s">
+      <c r="H223" t="s">
         <v>1754</v>
       </c>
-      <c r="I223" s="5" t="s">
+      <c r="I223" t="s">
         <v>1755</v>
       </c>
-      <c r="J223" s="5">
+      <c r="J223">
         <v>2000</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A224" s="5" t="s">
+      <c r="A224" t="s">
         <v>1696</v>
       </c>
-      <c r="B224" s="5" t="s">
+      <c r="B224" t="s">
         <v>6</v>
       </c>
-      <c r="C224" s="5" t="s">
+      <c r="C224" t="s">
         <v>1756</v>
       </c>
-      <c r="D224" s="5" t="s">
+      <c r="D224" t="s">
         <v>1757</v>
       </c>
-      <c r="E224" s="5" t="s">
+      <c r="E224" t="s">
         <v>1758</v>
       </c>
-      <c r="F224" s="5" t="s">
+      <c r="F224" t="s">
         <v>1759</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" t="s">
         <v>1760</v>
       </c>
-      <c r="H224" s="5" t="s">
+      <c r="H224" t="s">
         <v>1761</v>
       </c>
-      <c r="I224" s="5" t="s">
+      <c r="I224" t="s">
         <v>1762</v>
       </c>
-      <c r="J224" s="5">
+      <c r="J224">
         <v>2000</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A225" s="5" t="s">
+      <c r="A225" t="s">
         <v>1763</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" t="s">
         <v>89</v>
       </c>
-      <c r="C225" s="5" t="s">
+      <c r="C225" t="s">
         <v>1764</v>
       </c>
-      <c r="D225" s="5" t="s">
+      <c r="D225" t="s">
         <v>1765</v>
       </c>
-      <c r="E225" s="5" t="s">
+      <c r="E225" t="s">
         <v>1766</v>
       </c>
-      <c r="F225" s="5" t="s">
+      <c r="F225" t="s">
         <v>1767</v>
       </c>
-      <c r="G225" s="5" t="s">
+      <c r="G225" t="s">
         <v>1768</v>
       </c>
-      <c r="H225" s="5" t="s">
+      <c r="H225" t="s">
         <v>138</v>
       </c>
-      <c r="I225" s="5" t="s">
+      <c r="I225" t="s">
         <v>1769</v>
       </c>
-      <c r="J225" s="5">
+      <c r="J225">
         <v>1000</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A226" s="5" t="s">
+      <c r="A226" t="s">
         <v>1697</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" t="s">
         <v>6</v>
       </c>
-      <c r="C226" s="5" t="s">
+      <c r="C226" t="s">
         <v>1770</v>
       </c>
-      <c r="D226" s="5" t="s">
+      <c r="D226" t="s">
         <v>1771</v>
       </c>
-      <c r="E226" s="5" t="s">
+      <c r="E226" t="s">
         <v>1772</v>
       </c>
-      <c r="F226" s="5" t="s">
+      <c r="F226" t="s">
         <v>1773</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" t="s">
         <v>1774</v>
       </c>
-      <c r="H226" s="5" t="s">
+      <c r="H226" t="s">
         <v>1775</v>
       </c>
-      <c r="I226" s="5" t="s">
+      <c r="I226" t="s">
         <v>1776</v>
       </c>
-      <c r="J226" s="5">
+      <c r="J226">
         <v>5000</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A227" s="5" t="s">
+      <c r="A227" t="s">
         <v>1777</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" t="s">
         <v>12</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="C227" t="s">
         <v>1778</v>
       </c>
-      <c r="D227" s="5" t="s">
+      <c r="D227" t="s">
         <v>1779</v>
       </c>
-      <c r="E227" s="5" t="s">
+      <c r="E227" t="s">
         <v>1780</v>
       </c>
-      <c r="F227" s="5" t="s">
+      <c r="F227" t="s">
         <v>1781</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="G227" t="s">
         <v>1782</v>
       </c>
-      <c r="H227" s="5" t="s">
+      <c r="H227" t="s">
         <v>1783</v>
       </c>
-      <c r="I227" s="5" t="s">
+      <c r="I227" t="s">
         <v>1784</v>
       </c>
-      <c r="J227" s="5">
+      <c r="J227">
         <v>12000</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A228" s="5" t="s">
+      <c r="A228" t="s">
         <v>1785</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" t="s">
         <v>15</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" t="s">
         <v>33</v>
       </c>
-      <c r="D228" s="5" t="s">
+      <c r="D228" t="s">
         <v>1786</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="E228" t="s">
         <v>1787</v>
       </c>
-      <c r="F228" s="5" t="s">
+      <c r="F228" t="s">
         <v>1788</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" t="s">
         <v>1789</v>
       </c>
-      <c r="H228" s="5" t="s">
+      <c r="H228" t="s">
         <v>1790</v>
       </c>
-      <c r="I228" s="5" t="s">
+      <c r="I228" t="s">
         <v>1791</v>
       </c>
-      <c r="J228" s="5">
+      <c r="J228">
         <v>4000</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A229" s="5" t="s">
+      <c r="A229" t="s">
         <v>1698</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" t="s">
         <v>6</v>
       </c>
-      <c r="C229" s="5" t="s">
+      <c r="C229" t="s">
         <v>1792</v>
       </c>
-      <c r="D229" s="5" t="s">
+      <c r="D229" t="s">
         <v>1793</v>
       </c>
-      <c r="E229" s="5" t="s">
+      <c r="E229" t="s">
         <v>1794</v>
       </c>
-      <c r="F229" s="5" t="s">
+      <c r="F229" t="s">
         <v>1795</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="G229" t="s">
         <v>1796</v>
       </c>
-      <c r="H229" s="5" t="s">
+      <c r="H229" t="s">
         <v>1797</v>
       </c>
-      <c r="I229" s="5" t="s">
+      <c r="I229" t="s">
         <v>1798</v>
       </c>
-      <c r="J229" s="5">
+      <c r="J229">
         <v>8000</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A230" s="5" t="s">
+      <c r="A230" t="s">
         <v>1699</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B230" t="s">
         <v>15</v>
       </c>
-      <c r="C230" s="5" t="s">
+      <c r="C230" t="s">
         <v>1799</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D230" t="s">
         <v>1800</v>
       </c>
-      <c r="E230" s="5" t="s">
+      <c r="E230" t="s">
         <v>1801</v>
       </c>
-      <c r="F230" s="5" t="s">
+      <c r="F230" t="s">
         <v>1802</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="G230" t="s">
         <v>1803</v>
       </c>
-      <c r="H230" s="5" t="s">
+      <c r="H230" t="s">
         <v>1804</v>
       </c>
-      <c r="I230" s="5" t="s">
+      <c r="I230" t="s">
         <v>1805</v>
       </c>
-      <c r="J230" s="5">
+      <c r="J230">
         <v>2000</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A231" s="5" t="s">
+      <c r="A231" t="s">
         <v>1700</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B231" t="s">
         <v>89</v>
       </c>
-      <c r="C231" s="5" t="s">
+      <c r="C231" t="s">
         <v>1806</v>
       </c>
-      <c r="D231" s="5" t="s">
+      <c r="D231" t="s">
         <v>1807</v>
       </c>
-      <c r="E231" s="5" t="s">
+      <c r="E231" t="s">
         <v>1808</v>
       </c>
-      <c r="F231" s="5" t="s">
+      <c r="F231" t="s">
         <v>1809</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="G231" t="s">
         <v>1810</v>
       </c>
-      <c r="H231" s="5" t="s">
+      <c r="H231" t="s">
         <v>1811</v>
       </c>
-      <c r="I231" s="5" t="s">
+      <c r="I231" t="s">
         <v>1812</v>
       </c>
-      <c r="J231" s="5">
+      <c r="J231">
         <v>2000</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A232" s="5" t="s">
+      <c r="A232" t="s">
         <v>1701</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B232" t="s">
         <v>6</v>
       </c>
-      <c r="C232" s="5" t="s">
+      <c r="C232" t="s">
         <v>1813</v>
       </c>
-      <c r="D232" s="5" t="s">
+      <c r="D232" t="s">
         <v>1814</v>
       </c>
-      <c r="E232" s="5" t="s">
+      <c r="E232" t="s">
         <v>1815</v>
       </c>
-      <c r="F232" s="5" t="s">
+      <c r="F232" t="s">
         <v>1816</v>
       </c>
-      <c r="G232" s="5" t="s">
+      <c r="G232" t="s">
         <v>1817</v>
       </c>
-      <c r="H232" s="5" t="s">
+      <c r="H232" t="s">
         <v>1818</v>
       </c>
-      <c r="I232" s="5" t="s">
+      <c r="I232" t="s">
         <v>1819</v>
       </c>
-      <c r="J232" s="5">
+      <c r="J232">
         <v>5000</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A233" s="5" t="s">
+      <c r="A233" t="s">
         <v>1702</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B233" t="s">
         <v>15</v>
       </c>
-      <c r="C233" s="5" t="s">
+      <c r="C233" t="s">
         <v>1820</v>
       </c>
-      <c r="D233" s="5" t="s">
+      <c r="D233" t="s">
         <v>1821</v>
       </c>
-      <c r="E233" s="5" t="s">
+      <c r="E233" t="s">
         <v>1822</v>
       </c>
-      <c r="F233" s="5" t="s">
+      <c r="F233" t="s">
         <v>1823</v>
       </c>
-      <c r="G233" s="5" t="s">
+      <c r="G233" t="s">
         <v>1824</v>
       </c>
-      <c r="H233" s="5" t="s">
+      <c r="H233" t="s">
         <v>1825</v>
       </c>
-      <c r="I233" s="5" t="s">
+      <c r="I233" t="s">
         <v>1826</v>
       </c>
-      <c r="J233" s="5">
+      <c r="J233">
         <v>2000</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A234" s="5" t="s">
+      <c r="A234" t="s">
         <v>1703</v>
       </c>
-      <c r="B234" s="5" t="s">
+      <c r="B234" t="s">
         <v>12</v>
       </c>
-      <c r="C234" s="5" t="s">
+      <c r="C234" t="s">
         <v>1827</v>
       </c>
-      <c r="D234" s="5" t="s">
+      <c r="D234" t="s">
         <v>1828</v>
       </c>
-      <c r="E234" s="5" t="s">
+      <c r="E234" t="s">
         <v>1829</v>
       </c>
-      <c r="F234" s="5" t="s">
+      <c r="F234" t="s">
         <v>1830</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" t="s">
         <v>1831</v>
       </c>
-      <c r="H234" s="5" t="s">
+      <c r="H234" t="s">
         <v>1832</v>
       </c>
-      <c r="I234" s="5" t="s">
+      <c r="I234" t="s">
         <v>1833</v>
       </c>
-      <c r="J234" s="5">
+      <c r="J234">
         <v>12000</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A235" s="5" t="s">
+      <c r="A235" t="s">
         <v>1704</v>
       </c>
-      <c r="B235" s="5" t="s">
+      <c r="B235" t="s">
         <v>35</v>
       </c>
-      <c r="C235" s="5" t="s">
+      <c r="C235" t="s">
         <v>1834</v>
       </c>
-      <c r="D235" s="5" t="s">
+      <c r="D235" t="s">
         <v>1835</v>
       </c>
-      <c r="E235" s="5" t="s">
+      <c r="E235" t="s">
         <v>1836</v>
       </c>
-      <c r="F235" s="5" t="s">
+      <c r="F235" t="s">
         <v>1837</v>
       </c>
-      <c r="G235" s="5" t="s">
+      <c r="G235" t="s">
         <v>1838</v>
       </c>
-      <c r="H235" s="5" t="s">
+      <c r="H235" t="s">
         <v>1839</v>
       </c>
-      <c r="I235" s="5" t="s">
+      <c r="I235" t="s">
         <v>1840</v>
       </c>
-      <c r="J235" s="5">
+      <c r="J235">
         <v>3000</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A236" s="5" t="s">
+      <c r="A236" t="s">
         <v>139</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="B236" t="s">
         <v>15</v>
       </c>
-      <c r="C236" s="5" t="s">
+      <c r="C236" t="s">
         <v>1841</v>
       </c>
-      <c r="D236" s="5" t="s">
+      <c r="D236" t="s">
         <v>1842</v>
       </c>
-      <c r="E236" s="5" t="s">
+      <c r="E236" t="s">
         <v>1843</v>
       </c>
-      <c r="F236" s="5" t="s">
+      <c r="F236" t="s">
         <v>1844</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" t="s">
         <v>1078</v>
       </c>
-      <c r="H236" s="5" t="s">
+      <c r="H236" t="s">
         <v>1845</v>
       </c>
-      <c r="I236" s="5" t="s">
+      <c r="I236" t="s">
         <v>1846</v>
       </c>
-      <c r="J236" s="5">
+      <c r="J236">
         <v>2000</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A237" s="5" t="s">
+      <c r="A237" t="s">
         <v>1705</v>
       </c>
-      <c r="B237" s="5" t="s">
+      <c r="B237" t="s">
         <v>15</v>
       </c>
-      <c r="C237" s="5" t="s">
+      <c r="C237" t="s">
         <v>1847</v>
       </c>
-      <c r="D237" s="5" t="s">
+      <c r="D237" t="s">
         <v>1848</v>
       </c>
-      <c r="E237" s="5" t="s">
+      <c r="E237" t="s">
         <v>1849</v>
       </c>
-      <c r="F237" s="5" t="s">
+      <c r="F237" t="s">
         <v>1850</v>
       </c>
-      <c r="G237" s="5" t="s">
+      <c r="G237" t="s">
         <v>1851</v>
       </c>
-      <c r="H237" s="5" t="s">
+      <c r="H237" t="s">
         <v>1852</v>
       </c>
-      <c r="I237" s="5" t="s">
+      <c r="I237" t="s">
         <v>1853</v>
       </c>
-      <c r="J237" s="5">
+      <c r="J237">
         <v>4000</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A238" s="5" t="s">
+      <c r="A238" t="s">
         <v>1706</v>
       </c>
-      <c r="B238" s="5" t="s">
+      <c r="B238" t="s">
         <v>12</v>
       </c>
-      <c r="C238" s="5" t="s">
+      <c r="C238" t="s">
         <v>1854</v>
       </c>
-      <c r="D238" s="5" t="s">
+      <c r="D238" t="s">
         <v>1855</v>
       </c>
-      <c r="E238" s="5" t="s">
+      <c r="E238" t="s">
         <v>1856</v>
       </c>
-      <c r="F238" s="5" t="s">
+      <c r="F238" t="s">
         <v>1857</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" t="s">
         <v>1858</v>
       </c>
-      <c r="H238" s="5" t="s">
+      <c r="H238" t="s">
         <v>1859</v>
       </c>
-      <c r="I238" s="5" t="s">
+      <c r="I238" t="s">
         <v>1860</v>
       </c>
-      <c r="J238" s="5">
+      <c r="J238">
         <v>7000</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A239" s="5" t="s">
+      <c r="A239" t="s">
         <v>1707</v>
       </c>
-      <c r="B239" s="5" t="s">
+      <c r="B239" t="s">
         <v>6</v>
       </c>
-      <c r="C239" s="5" t="s">
+      <c r="C239" t="s">
         <v>1861</v>
       </c>
-      <c r="D239" s="5" t="s">
+      <c r="D239" t="s">
         <v>1862</v>
       </c>
-      <c r="E239" s="5" t="s">
+      <c r="E239" t="s">
         <v>1863</v>
       </c>
-      <c r="F239" s="5" t="s">
+      <c r="F239" t="s">
         <v>1864</v>
       </c>
-      <c r="G239" s="5" t="s">
+      <c r="G239" t="s">
         <v>1865</v>
       </c>
-      <c r="H239" s="5" t="s">
+      <c r="H239" t="s">
         <v>1866</v>
       </c>
-      <c r="I239" s="5" t="s">
+      <c r="I239" t="s">
         <v>1867</v>
       </c>
-      <c r="J239" s="5">
+      <c r="J239">
         <v>4000</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A240" s="5" t="s">
+      <c r="A240" t="s">
         <v>1708</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240" s="5" t="s">
+      <c r="C240" t="s">
         <v>1868</v>
       </c>
-      <c r="D240" s="5" t="s">
+      <c r="D240" t="s">
         <v>1869</v>
       </c>
-      <c r="E240" s="5" t="s">
+      <c r="E240" t="s">
         <v>1870</v>
       </c>
-      <c r="F240" s="5" t="s">
+      <c r="F240" t="s">
         <v>1871</v>
       </c>
-      <c r="G240" s="5" t="s">
+      <c r="G240" t="s">
         <v>1872</v>
       </c>
-      <c r="H240" s="5" t="s">
+      <c r="H240" t="s">
         <v>1873</v>
       </c>
-      <c r="I240" s="5" t="s">
+      <c r="I240" t="s">
         <v>1874</v>
       </c>
-      <c r="J240" s="5">
+      <c r="J240">
         <v>7000</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A241" s="5" t="s">
+      <c r="A241" t="s">
         <v>1709</v>
       </c>
-      <c r="B241" s="5" t="s">
+      <c r="B241" t="s">
         <v>5</v>
       </c>
-      <c r="C241" s="5" t="s">
+      <c r="C241" t="s">
         <v>1875</v>
       </c>
-      <c r="D241" s="5" t="s">
+      <c r="D241" t="s">
         <v>1876</v>
       </c>
-      <c r="E241" s="5" t="s">
+      <c r="E241" t="s">
         <v>1877</v>
       </c>
-      <c r="F241" s="5" t="s">
+      <c r="F241" t="s">
         <v>1878</v>
       </c>
-      <c r="G241" s="5" t="s">
+      <c r="G241" t="s">
         <v>1879</v>
       </c>
-      <c r="H241" s="5" t="s">
+      <c r="H241" t="s">
         <v>138</v>
       </c>
-      <c r="I241" s="5" t="s">
+      <c r="I241" t="s">
         <v>1880</v>
       </c>
-      <c r="J241" s="5">
+      <c r="J241">
         <v>9000</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A242" s="5" t="s">
+      <c r="A242" t="s">
         <v>1710</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="B242" t="s">
         <v>12</v>
       </c>
-      <c r="C242" s="5" t="s">
+      <c r="C242" t="s">
         <v>1881</v>
       </c>
-      <c r="D242" s="5" t="s">
+      <c r="D242" t="s">
         <v>1882</v>
       </c>
-      <c r="E242" s="5" t="s">
+      <c r="E242" t="s">
         <v>1883</v>
       </c>
-      <c r="F242" s="5" t="s">
+      <c r="F242" t="s">
         <v>1884</v>
       </c>
-      <c r="G242" s="5" t="s">
+      <c r="G242" t="s">
         <v>1885</v>
       </c>
-      <c r="H242" s="5" t="s">
+      <c r="H242" t="s">
         <v>1886</v>
       </c>
-      <c r="I242" s="5" t="s">
+      <c r="I242" t="s">
         <v>1887</v>
       </c>
-      <c r="J242" s="5">
+      <c r="J242">
         <v>7000</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A243" s="5" t="s">
+      <c r="A243" t="s">
         <v>1711</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="B243" t="s">
         <v>6</v>
       </c>
-      <c r="C243" s="5" t="s">
+      <c r="C243" t="s">
         <v>1888</v>
       </c>
-      <c r="D243" s="5" t="s">
+      <c r="D243" t="s">
         <v>1889</v>
       </c>
-      <c r="E243" s="5" t="s">
+      <c r="E243" t="s">
         <v>1890</v>
       </c>
-      <c r="F243" s="5" t="s">
+      <c r="F243" t="s">
         <v>1891</v>
       </c>
-      <c r="G243" s="5" t="s">
+      <c r="G243" t="s">
         <v>1892</v>
       </c>
-      <c r="H243" s="5" t="s">
+      <c r="H243" t="s">
         <v>1893</v>
       </c>
-      <c r="I243" s="5" t="s">
+      <c r="I243" t="s">
         <v>1894</v>
       </c>
-      <c r="J243" s="5">
+      <c r="J243">
         <v>4000</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A244" s="5" t="s">
+      <c r="A244" t="s">
         <v>1712</v>
       </c>
-      <c r="B244" s="5" t="s">
+      <c r="B244" t="s">
         <v>1895</v>
       </c>
-      <c r="C244" s="5" t="s">
+      <c r="C244" t="s">
         <v>1896</v>
       </c>
-      <c r="D244" s="5" t="s">
+      <c r="D244" t="s">
         <v>1897</v>
       </c>
-      <c r="E244" s="5" t="s">
+      <c r="E244" t="s">
         <v>1898</v>
       </c>
-      <c r="F244" s="5" t="s">
+      <c r="F244" t="s">
         <v>1899</v>
       </c>
-      <c r="G244" s="5" t="s">
+      <c r="G244" t="s">
         <v>1900</v>
       </c>
-      <c r="H244" s="5" t="s">
+      <c r="H244" t="s">
         <v>1901</v>
       </c>
-      <c r="I244" s="5" t="s">
+      <c r="I244" t="s">
         <v>1902</v>
       </c>
-      <c r="J244" s="5">
+      <c r="J244">
         <v>2000</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A245" s="5" t="s">
+      <c r="A245" t="s">
         <v>1903</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" t="s">
         <v>15</v>
       </c>
-      <c r="C245" s="5" t="s">
+      <c r="C245" t="s">
         <v>1904</v>
       </c>
-      <c r="D245" s="5" t="s">
+      <c r="D245" t="s">
         <v>1905</v>
       </c>
-      <c r="E245" s="5" t="s">
+      <c r="E245" t="s">
         <v>1906</v>
       </c>
-      <c r="F245" s="5" t="s">
+      <c r="F245" t="s">
         <v>1907</v>
       </c>
-      <c r="G245" s="5" t="s">
+      <c r="G245" t="s">
         <v>1908</v>
       </c>
-      <c r="H245" s="5" t="s">
+      <c r="H245" t="s">
         <v>1909</v>
       </c>
-      <c r="I245" s="5" t="s">
+      <c r="I245" t="s">
         <v>1910</v>
       </c>
-      <c r="J245" s="5">
+      <c r="J245">
         <v>4000</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A246" s="5" t="s">
+      <c r="A246" t="s">
         <v>1713</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B246" t="s">
         <v>6</v>
       </c>
-      <c r="C246" s="5" t="s">
+      <c r="C246" t="s">
         <v>1911</v>
       </c>
-      <c r="D246" s="5" t="s">
+      <c r="D246" t="s">
         <v>1912</v>
       </c>
-      <c r="E246" s="5" t="s">
+      <c r="E246" t="s">
         <v>1913</v>
       </c>
-      <c r="F246" s="5" t="s">
+      <c r="F246" t="s">
         <v>1914</v>
       </c>
-      <c r="G246" s="5" t="s">
+      <c r="G246" t="s">
         <v>1915</v>
       </c>
-      <c r="H246" s="5" t="s">
+      <c r="H246" t="s">
         <v>1916</v>
       </c>
-      <c r="I246" s="5" t="s">
+      <c r="I246" t="s">
         <v>1917</v>
       </c>
-      <c r="J246" s="5">
+      <c r="J246">
         <v>5000</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A247" s="5" t="s">
+      <c r="A247" t="s">
         <v>197</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B247" t="s">
         <v>15</v>
       </c>
-      <c r="C247" s="5" t="s">
+      <c r="C247" t="s">
         <v>1918</v>
       </c>
-      <c r="D247" s="5" t="s">
+      <c r="D247" t="s">
         <v>1919</v>
       </c>
-      <c r="E247" s="5" t="s">
+      <c r="E247" t="s">
         <v>1920</v>
       </c>
-      <c r="F247" s="5" t="s">
+      <c r="F247" t="s">
         <v>1921</v>
       </c>
-      <c r="G247" s="5" t="s">
+      <c r="G247" t="s">
         <v>1922</v>
       </c>
-      <c r="H247" s="5" t="s">
+      <c r="H247" t="s">
         <v>1923</v>
       </c>
-      <c r="I247" s="5" t="s">
+      <c r="I247" t="s">
         <v>1924</v>
       </c>
-      <c r="J247" s="5">
+      <c r="J247">
         <v>2000</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A248" s="5" t="s">
+      <c r="A248" t="s">
         <v>109</v>
       </c>
-      <c r="B248" s="5" t="s">
+      <c r="B248" t="s">
         <v>6</v>
       </c>
-      <c r="C248" s="5" t="s">
+      <c r="C248" t="s">
         <v>1925</v>
       </c>
-      <c r="D248" s="5" t="s">
+      <c r="D248" t="s">
         <v>220</v>
       </c>
-      <c r="E248" s="5" t="s">
+      <c r="E248" t="s">
         <v>1926</v>
       </c>
-      <c r="F248" s="5" t="s">
+      <c r="F248" t="s">
         <v>1927</v>
       </c>
-      <c r="G248" s="5" t="s">
+      <c r="G248" t="s">
         <v>1928</v>
       </c>
-      <c r="H248" s="5" t="s">
+      <c r="H248" t="s">
         <v>1929</v>
       </c>
-      <c r="I248" s="5" t="s">
+      <c r="I248" t="s">
         <v>1930</v>
       </c>
-      <c r="J248" s="5">
+      <c r="J248">
         <v>3000</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A249" s="6" t="s">
+      <c r="A249" t="s">
         <v>1714</v>
       </c>
-      <c r="B249" s="6" t="s">
+      <c r="B249" t="s">
         <v>1931</v>
       </c>
-      <c r="C249" s="6" t="s">
+      <c r="C249" t="s">
         <v>1932</v>
       </c>
-      <c r="D249" s="6" t="s">
+      <c r="D249" t="s">
         <v>1933</v>
       </c>
-      <c r="E249" s="6" t="s">
+      <c r="E249" t="s">
         <v>1934</v>
       </c>
-      <c r="F249" s="6" t="s">
+      <c r="F249" t="s">
         <v>1935</v>
       </c>
-      <c r="G249" s="6" t="s">
+      <c r="G249" t="s">
         <v>1936</v>
       </c>
-      <c r="H249" s="6" t="s">
+      <c r="H249" t="s">
         <v>1937</v>
       </c>
-      <c r="I249" s="6" t="s">
+      <c r="I249" t="s">
         <v>1938</v>
       </c>
-      <c r="J249" s="6">
+      <c r="J249">
         <v>3000</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A250" s="6" t="s">
+      <c r="A250" t="s">
         <v>1715</v>
       </c>
-      <c r="B250" s="6" t="s">
+      <c r="B250" t="s">
         <v>15</v>
       </c>
-      <c r="C250" s="6" t="s">
+      <c r="C250" t="s">
         <v>1939</v>
       </c>
-      <c r="D250" s="6" t="s">
+      <c r="D250" t="s">
         <v>1940</v>
       </c>
-      <c r="E250" s="6" t="s">
+      <c r="E250" t="s">
         <v>1941</v>
       </c>
-      <c r="F250" s="6" t="s">
+      <c r="F250" t="s">
         <v>1942</v>
       </c>
-      <c r="G250" s="6" t="s">
+      <c r="G250" t="s">
         <v>1943</v>
       </c>
-      <c r="H250" s="6" t="s">
+      <c r="H250" t="s">
         <v>1944</v>
       </c>
-      <c r="I250" s="6" t="s">
+      <c r="I250" t="s">
         <v>1945</v>
       </c>
-      <c r="J250" s="6">
+      <c r="J250">
         <v>2000</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A251" s="6" t="s">
+      <c r="A251" t="s">
         <v>1716</v>
       </c>
-      <c r="B251" s="6" t="s">
+      <c r="B251" t="s">
         <v>6</v>
       </c>
-      <c r="C251" s="6" t="s">
+      <c r="C251" t="s">
         <v>1946</v>
       </c>
-      <c r="D251" s="6" t="s">
+      <c r="D251" t="s">
         <v>1947</v>
       </c>
-      <c r="E251" s="6" t="s">
+      <c r="E251" t="s">
         <v>1948</v>
       </c>
-      <c r="F251" s="6" t="s">
+      <c r="F251" t="s">
         <v>1949</v>
       </c>
-      <c r="G251" s="6" t="s">
+      <c r="G251" t="s">
         <v>1950</v>
       </c>
-      <c r="H251" s="6" t="s">
+      <c r="H251" t="s">
         <v>1951</v>
       </c>
-      <c r="I251" s="6" t="s">
+      <c r="I251" t="s">
         <v>1952</v>
       </c>
-      <c r="J251" s="6">
+      <c r="J251">
         <v>3000</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A252" s="6" t="s">
+      <c r="A252" t="s">
         <v>1717</v>
       </c>
-      <c r="B252" s="6" t="s">
+      <c r="B252" t="s">
         <v>73</v>
       </c>
-      <c r="C252" s="6" t="s">
+      <c r="C252" t="s">
         <v>1953</v>
       </c>
-      <c r="D252" s="6" t="s">
+      <c r="D252" t="s">
         <v>1954</v>
       </c>
-      <c r="E252" s="6" t="s">
+      <c r="E252" t="s">
         <v>1955</v>
       </c>
-      <c r="F252" s="6" t="s">
+      <c r="F252" t="s">
         <v>1956</v>
       </c>
-      <c r="G252" s="6" t="s">
+      <c r="G252" t="s">
         <v>1957</v>
       </c>
-      <c r="H252" s="6" t="s">
+      <c r="H252" t="s">
         <v>1958</v>
       </c>
-      <c r="I252" s="6" t="s">
+      <c r="I252" t="s">
         <v>1959</v>
       </c>
-      <c r="J252" s="6">
+      <c r="J252">
         <v>6000</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A253" s="6" t="s">
+      <c r="A253" t="s">
         <v>1718</v>
       </c>
-      <c r="B253" s="6" t="s">
+      <c r="B253" t="s">
         <v>10</v>
       </c>
-      <c r="C253" s="6" t="s">
+      <c r="C253" t="s">
         <v>1960</v>
       </c>
-      <c r="D253" s="6" t="s">
+      <c r="D253" t="s">
         <v>1961</v>
       </c>
-      <c r="E253" s="6" t="s">
+      <c r="E253" t="s">
         <v>1962</v>
       </c>
-      <c r="F253" s="6" t="s">
+      <c r="F253" t="s">
         <v>1963</v>
       </c>
-      <c r="G253" s="6" t="s">
+      <c r="G253" t="s">
         <v>1964</v>
       </c>
-      <c r="H253" s="6" t="s">
+      <c r="H253" t="s">
         <v>1965</v>
       </c>
-      <c r="I253" s="6" t="s">
+      <c r="I253" t="s">
         <v>1966</v>
       </c>
-      <c r="J253" s="6">
+      <c r="J253">
         <v>4000</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A254" s="6" t="s">
+      <c r="A254" t="s">
         <v>1719</v>
       </c>
-      <c r="B254" s="6" t="s">
+      <c r="B254" t="s">
         <v>1967</v>
       </c>
-      <c r="C254" s="6" t="s">
+      <c r="C254" t="s">
         <v>1968</v>
       </c>
-      <c r="D254" s="6" t="s">
+      <c r="D254" t="s">
         <v>1969</v>
       </c>
-      <c r="E254" s="6" t="s">
+      <c r="E254" t="s">
         <v>1970</v>
       </c>
-      <c r="F254" s="6" t="s">
+      <c r="F254" t="s">
         <v>1971</v>
       </c>
-      <c r="G254" s="6" t="s">
+      <c r="G254" t="s">
         <v>1972</v>
       </c>
-      <c r="H254" s="6" t="s">
+      <c r="H254" t="s">
         <v>138</v>
       </c>
-      <c r="I254" s="6" t="s">
+      <c r="I254" t="s">
         <v>1973</v>
       </c>
-      <c r="J254" s="6">
+      <c r="J254">
         <v>3000</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A255" s="6" t="s">
+      <c r="A255" t="s">
         <v>1720</v>
       </c>
-      <c r="B255" s="6" t="s">
+      <c r="B255" t="s">
         <v>1967</v>
       </c>
-      <c r="C255" s="6" t="s">
+      <c r="C255" t="s">
         <v>1974</v>
       </c>
-      <c r="D255" s="6" t="s">
+      <c r="D255" t="s">
         <v>1975</v>
       </c>
-      <c r="E255" s="6" t="s">
+      <c r="E255" t="s">
         <v>1976</v>
       </c>
-      <c r="F255" s="6" t="s">
+      <c r="F255" t="s">
         <v>1977</v>
       </c>
-      <c r="G255" s="6" t="s">
+      <c r="G255" t="s">
         <v>1978</v>
       </c>
-      <c r="H255" s="6" t="s">
+      <c r="H255" t="s">
         <v>138</v>
       </c>
-      <c r="I255" s="6" t="s">
+      <c r="I255" t="s">
         <v>1979</v>
       </c>
-      <c r="J255" s="6">
+      <c r="J255">
         <v>2000</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A256" s="6" t="s">
+      <c r="A256" t="s">
         <v>1721</v>
       </c>
-      <c r="B256" s="6" t="s">
+      <c r="B256" t="s">
         <v>35</v>
       </c>
-      <c r="C256" s="6" t="s">
+      <c r="C256" t="s">
         <v>1980</v>
       </c>
-      <c r="D256" s="6" t="s">
+      <c r="D256" t="s">
         <v>1981</v>
       </c>
-      <c r="E256" s="6" t="s">
+      <c r="E256" t="s">
         <v>1982</v>
       </c>
-      <c r="F256" s="6" t="s">
+      <c r="F256" t="s">
         <v>1983</v>
       </c>
-      <c r="G256" s="6" t="s">
+      <c r="G256" t="s">
         <v>1984</v>
       </c>
-      <c r="H256" s="6" t="s">
+      <c r="H256" t="s">
         <v>1985</v>
       </c>
-      <c r="I256" s="6" t="s">
+      <c r="I256" t="s">
         <v>1986</v>
       </c>
-      <c r="J256" s="6">
+      <c r="J256">
         <v>6000</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A257" s="6" t="s">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A257" t="s">
         <v>1722</v>
       </c>
-      <c r="B257" s="6" t="s">
+      <c r="B257" t="s">
         <v>12</v>
       </c>
-      <c r="C257" s="6" t="s">
+      <c r="C257" t="s">
         <v>1987</v>
       </c>
-      <c r="D257" s="6" t="s">
+      <c r="D257" t="s">
         <v>1988</v>
       </c>
-      <c r="E257" s="6" t="s">
+      <c r="E257" t="s">
         <v>1989</v>
       </c>
-      <c r="F257" s="6" t="s">
+      <c r="F257" t="s">
         <v>1990</v>
       </c>
-      <c r="G257" s="6" t="s">
+      <c r="G257" t="s">
         <v>1991</v>
       </c>
-      <c r="H257" s="6" t="s">
+      <c r="H257" t="s">
         <v>1992</v>
       </c>
-      <c r="I257" s="6" t="s">
+      <c r="I257" t="s">
         <v>1993</v>
       </c>
-      <c r="J257" s="6">
+      <c r="J257">
         <v>2000</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A258" s="6" t="s">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A258" t="s">
         <v>1723</v>
       </c>
-      <c r="B258" s="6" t="s">
+      <c r="B258" t="s">
         <v>1931</v>
       </c>
-      <c r="C258" s="6" t="s">
+      <c r="C258" t="s">
         <v>1994</v>
       </c>
-      <c r="D258" s="6" t="s">
+      <c r="D258" t="s">
         <v>1995</v>
       </c>
-      <c r="E258" s="6" t="s">
+      <c r="E258" t="s">
         <v>1996</v>
       </c>
-      <c r="F258" s="6" t="s">
+      <c r="F258" t="s">
         <v>1997</v>
       </c>
-      <c r="G258" s="6" t="s">
+      <c r="G258" t="s">
         <v>1998</v>
       </c>
-      <c r="H258" s="6" t="s">
+      <c r="H258" t="s">
         <v>1999</v>
       </c>
-      <c r="I258" s="6" t="s">
+      <c r="I258" t="s">
         <v>2000</v>
       </c>
-      <c r="J258" s="6">
+      <c r="J258">
         <v>2000</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A259" s="6" t="s">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A259" t="s">
         <v>1724</v>
       </c>
-      <c r="B259" s="6" t="s">
+      <c r="B259" t="s">
         <v>10</v>
       </c>
-      <c r="C259" s="6" t="s">
+      <c r="C259" t="s">
         <v>2001</v>
       </c>
-      <c r="D259" s="6" t="s">
+      <c r="D259" t="s">
         <v>2002</v>
       </c>
-      <c r="E259" s="6" t="s">
+      <c r="E259" t="s">
         <v>2003</v>
       </c>
-      <c r="F259" s="6" t="s">
+      <c r="F259" t="s">
         <v>2004</v>
       </c>
-      <c r="G259" s="6" t="s">
+      <c r="G259" t="s">
         <v>2005</v>
       </c>
-      <c r="H259" s="6" t="s">
+      <c r="H259" t="s">
         <v>2006</v>
       </c>
-      <c r="I259" s="6" t="s">
+      <c r="I259" t="s">
         <v>2007</v>
       </c>
-      <c r="J259" s="6">
+      <c r="J259">
         <v>1000</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A260" s="6" t="s">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A260" t="s">
         <v>1725</v>
       </c>
-      <c r="B260" s="6" t="s">
+      <c r="B260" t="s">
         <v>6</v>
       </c>
-      <c r="C260" s="6" t="s">
+      <c r="C260" t="s">
         <v>2008</v>
       </c>
-      <c r="D260" s="6" t="s">
+      <c r="D260" t="s">
         <v>2009</v>
       </c>
-      <c r="E260" s="6" t="s">
+      <c r="E260" t="s">
         <v>2010</v>
       </c>
-      <c r="F260" s="6" t="s">
+      <c r="F260" t="s">
         <v>2011</v>
       </c>
-      <c r="G260" s="6" t="s">
+      <c r="G260" t="s">
         <v>2012</v>
       </c>
-      <c r="H260" s="6" t="s">
+      <c r="H260" t="s">
         <v>2013</v>
       </c>
-      <c r="I260" s="6" t="s">
+      <c r="I260" t="s">
         <v>2014</v>
       </c>
-      <c r="J260" s="6">
+      <c r="J260">
         <v>4000</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A261" s="6" t="s">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A261" t="s">
         <v>1726</v>
       </c>
-      <c r="B261" s="6" t="s">
+      <c r="B261" t="s">
         <v>6</v>
       </c>
-      <c r="C261" s="6" t="s">
+      <c r="C261" t="s">
         <v>2015</v>
       </c>
-      <c r="D261" s="6" t="s">
+      <c r="D261" t="s">
         <v>2016</v>
       </c>
-      <c r="E261" s="6" t="s">
+      <c r="E261" t="s">
         <v>2017</v>
       </c>
-      <c r="F261" s="6" t="s">
+      <c r="F261" t="s">
         <v>2018</v>
       </c>
-      <c r="G261" s="6" t="s">
+      <c r="G261" t="s">
         <v>2019</v>
       </c>
-      <c r="H261" s="6" t="s">
+      <c r="H261" t="s">
         <v>2020</v>
       </c>
-      <c r="I261" s="6" t="s">
+      <c r="I261" t="s">
         <v>2021</v>
       </c>
-      <c r="J261" s="6">
+      <c r="J261">
         <v>7000</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A262" s="6" t="s">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A262" t="s">
         <v>1727</v>
       </c>
-      <c r="B262" s="6" t="s">
+      <c r="B262" t="s">
         <v>12</v>
       </c>
-      <c r="C262" s="6" t="s">
+      <c r="C262" t="s">
         <v>2022</v>
       </c>
-      <c r="D262" s="6" t="s">
+      <c r="D262" t="s">
         <v>2023</v>
       </c>
-      <c r="E262" s="6" t="s">
+      <c r="E262" t="s">
         <v>2024</v>
       </c>
-      <c r="F262" s="6" t="s">
+      <c r="F262" t="s">
         <v>2025</v>
       </c>
-      <c r="G262" s="6" t="s">
+      <c r="G262" t="s">
         <v>2026</v>
       </c>
-      <c r="H262" s="6" t="s">
+      <c r="H262" t="s">
         <v>2027</v>
       </c>
-      <c r="I262" s="6" t="s">
+      <c r="I262" t="s">
         <v>2028</v>
       </c>
-      <c r="J262" s="6">
+      <c r="J262">
         <v>9000</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A263" s="6" t="s">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A263" t="s">
         <v>2029</v>
       </c>
-      <c r="B263" s="6" t="s">
+      <c r="B263" t="s">
         <v>12</v>
       </c>
-      <c r="C263" s="6" t="s">
+      <c r="C263" t="s">
         <v>2022</v>
       </c>
-      <c r="D263" s="6" t="s">
+      <c r="D263" t="s">
         <v>2030</v>
       </c>
-      <c r="E263" s="6" t="s">
+      <c r="E263" t="s">
         <v>2031</v>
       </c>
-      <c r="F263" s="6" t="s">
+      <c r="F263" t="s">
         <v>2032</v>
       </c>
-      <c r="G263" s="6" t="s">
+      <c r="G263" t="s">
         <v>2033</v>
       </c>
-      <c r="H263" s="6" t="s">
+      <c r="H263" t="s">
         <v>2033</v>
       </c>
-      <c r="I263" s="6" t="s">
+      <c r="I263" t="s">
         <v>2034</v>
       </c>
-      <c r="J263" s="6">
+      <c r="J263">
         <v>9000</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A264" s="6" t="s">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A264" t="s">
         <v>1728</v>
       </c>
-      <c r="B264" s="6" t="s">
+      <c r="B264" t="s">
         <v>6</v>
       </c>
-      <c r="C264" s="6" t="s">
+      <c r="C264" t="s">
         <v>2035</v>
       </c>
-      <c r="D264" s="6" t="s">
+      <c r="D264" t="s">
         <v>2036</v>
       </c>
-      <c r="E264" s="6" t="s">
+      <c r="E264" t="s">
         <v>2037</v>
       </c>
-      <c r="F264" s="6" t="s">
+      <c r="F264" t="s">
         <v>2038</v>
       </c>
-      <c r="G264" s="6" t="s">
+      <c r="G264" t="s">
         <v>2039</v>
       </c>
-      <c r="H264" s="6" t="s">
+      <c r="H264" t="s">
         <v>2040</v>
       </c>
-      <c r="I264" s="6" t="s">
+      <c r="I264" t="s">
         <v>2041</v>
       </c>
-      <c r="J264" s="6">
+      <c r="J264">
         <v>12000</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A265" s="6" t="s">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A265" t="s">
         <v>1729</v>
       </c>
-      <c r="B265" s="6" t="s">
+      <c r="B265" t="s">
         <v>6</v>
       </c>
-      <c r="C265" s="6" t="s">
+      <c r="C265" t="s">
         <v>2042</v>
       </c>
-      <c r="D265" s="6" t="s">
+      <c r="D265" t="s">
         <v>2043</v>
       </c>
-      <c r="E265" s="6" t="s">
+      <c r="E265" t="s">
         <v>2044</v>
       </c>
-      <c r="F265" s="6" t="s">
+      <c r="F265" t="s">
         <v>2045</v>
       </c>
-      <c r="G265" s="6" t="s">
+      <c r="G265" t="s">
         <v>2046</v>
       </c>
-      <c r="H265" s="6" t="s">
+      <c r="H265" t="s">
         <v>2047</v>
       </c>
-      <c r="I265" s="6" t="s">
+      <c r="I265" t="s">
         <v>2048</v>
       </c>
-      <c r="J265" s="6">
+      <c r="J265">
         <v>7000</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A266" s="6" t="s">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A266" t="s">
         <v>1730</v>
       </c>
-      <c r="B266" s="6" t="s">
+      <c r="B266" t="s">
         <v>15</v>
       </c>
-      <c r="C266" s="6" t="s">
+      <c r="C266" t="s">
         <v>2049</v>
       </c>
-      <c r="D266" s="6" t="s">
+      <c r="D266" t="s">
         <v>2050</v>
       </c>
-      <c r="E266" s="6" t="s">
+      <c r="E266" t="s">
         <v>2051</v>
       </c>
-      <c r="F266" s="6" t="s">
+      <c r="F266" t="s">
         <v>2052</v>
       </c>
-      <c r="G266" s="6" t="s">
+      <c r="G266" t="s">
         <v>2053</v>
       </c>
-      <c r="H266" s="6" t="s">
+      <c r="H266" t="s">
         <v>2054</v>
       </c>
-      <c r="I266" s="6" t="s">
+      <c r="I266" t="s">
         <v>2055</v>
       </c>
-      <c r="J266" s="6">
+      <c r="J266">
         <v>1000</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A267" s="6" t="s">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A267" t="s">
         <v>1731</v>
       </c>
-      <c r="B267" s="6" t="s">
+      <c r="B267" t="s">
         <v>6</v>
       </c>
-      <c r="C267" s="6" t="s">
+      <c r="C267" t="s">
         <v>2056</v>
       </c>
-      <c r="D267" s="6" t="s">
+      <c r="D267" t="s">
         <v>2057</v>
       </c>
-      <c r="E267" s="6" t="s">
+      <c r="E267" t="s">
         <v>2058</v>
       </c>
-      <c r="F267" s="6" t="s">
+      <c r="F267" t="s">
         <v>2059</v>
       </c>
-      <c r="G267" s="6" t="s">
+      <c r="G267" t="s">
         <v>2060</v>
       </c>
-      <c r="H267" s="6" t="s">
+      <c r="H267" t="s">
         <v>2061</v>
       </c>
-      <c r="I267" s="6" t="s">
+      <c r="I267" t="s">
         <v>2062</v>
       </c>
-      <c r="J267" s="6">
+      <c r="J267">
         <v>3000</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A268" s="6" t="s">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A268" t="s">
         <v>1732</v>
       </c>
-      <c r="B268" s="6" t="s">
+      <c r="B268" t="s">
         <v>15</v>
       </c>
-      <c r="C268" s="6" t="s">
+      <c r="C268" t="s">
         <v>2063</v>
       </c>
-      <c r="D268" s="6" t="s">
+      <c r="D268" t="s">
         <v>2064</v>
       </c>
-      <c r="E268" s="6" t="s">
+      <c r="E268" t="s">
         <v>2065</v>
       </c>
-      <c r="F268" s="6" t="s">
+      <c r="F268" t="s">
         <v>2066</v>
       </c>
-      <c r="G268" s="6" t="s">
+      <c r="G268" t="s">
         <v>2067</v>
       </c>
-      <c r="H268" s="6" t="s">
+      <c r="H268" t="s">
         <v>2068</v>
       </c>
-      <c r="I268" s="6" t="s">
+      <c r="I268" t="s">
         <v>2069</v>
       </c>
-      <c r="J268" s="6">
+      <c r="J268">
         <v>2000</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A269" s="6" t="s">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A269" t="s">
         <v>1733</v>
       </c>
-      <c r="B269" s="6" t="s">
+      <c r="B269" t="s">
         <v>6</v>
       </c>
-      <c r="C269" s="6" t="s">
+      <c r="C269" t="s">
         <v>2070</v>
       </c>
-      <c r="D269" s="6" t="s">
+      <c r="D269" t="s">
         <v>2071</v>
       </c>
-      <c r="E269" s="6" t="s">
+      <c r="E269" t="s">
         <v>2072</v>
       </c>
-      <c r="F269" s="6" t="s">
+      <c r="F269" t="s">
         <v>2073</v>
       </c>
-      <c r="G269" s="6" t="s">
+      <c r="G269" t="s">
         <v>2074</v>
       </c>
-      <c r="H269" s="6" t="s">
+      <c r="H269" t="s">
         <v>2075</v>
       </c>
-      <c r="I269" s="6" t="s">
+      <c r="I269" t="s">
         <v>2076</v>
       </c>
-      <c r="J269" s="6">
+      <c r="J269">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A270" s="5" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H270" s="5" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I270" s="5" t="s">
+        <v>2100</v>
+      </c>
+      <c r="J270" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="K270" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A271" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H271" s="5" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I271" s="5" t="s">
+        <v>2106</v>
+      </c>
+      <c r="J271" s="5" t="s">
+        <v>2107</v>
+      </c>
+      <c r="K271" s="5">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A272" s="5" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>2112</v>
+      </c>
+      <c r="H272" s="5" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I272" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J272" s="5" t="s">
+        <v>2114</v>
+      </c>
+      <c r="K272" s="5">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A273" s="5" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>2119</v>
+      </c>
+      <c r="H273" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I273" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="J273" s="5" t="s">
+        <v>2122</v>
+      </c>
+      <c r="K273" s="5">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A274" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>2124</v>
+      </c>
+      <c r="G274" s="5" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="I274" s="5" t="s">
+        <v>2126</v>
+      </c>
+      <c r="J274" s="5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="K274" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A275" s="5" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>2132</v>
+      </c>
+      <c r="G275" s="5" t="s">
+        <v>2133</v>
+      </c>
+      <c r="H275" s="5" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I275" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J275" s="5" t="s">
+        <v>2135</v>
+      </c>
+      <c r="K275" s="5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A276" s="5" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E276" s="5" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>2140</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="H276" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I276" s="5" t="s">
+        <v>2143</v>
+      </c>
+      <c r="J276" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="K276" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A277" s="5" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I277" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J277" s="5" t="s">
+        <v>2152</v>
+      </c>
+      <c r="K277" s="5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A278" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E278" s="5" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>2158</v>
+      </c>
+      <c r="H278" s="5" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I278" s="5" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J278" s="5" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K278" s="5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A279" s="5" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E279" s="5" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="H279" s="5" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I279" s="5" t="s">
+        <v>2168</v>
+      </c>
+      <c r="J279" s="5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="K279" s="5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A280" s="5" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E280" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>2174</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>2175</v>
+      </c>
+      <c r="H280" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I280" s="5" t="s">
+        <v>2177</v>
+      </c>
+      <c r="J280" s="5" t="s">
+        <v>2178</v>
+      </c>
+      <c r="K280" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A281" s="5" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>2184</v>
+      </c>
+      <c r="H281" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I281" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="J281" s="5" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K281" s="5">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A282" s="5" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>2193</v>
+      </c>
+      <c r="H282" s="5" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I282" s="5" t="s">
+        <v>2195</v>
+      </c>
+      <c r="J282" s="5" t="s">
+        <v>2196</v>
+      </c>
+      <c r="K282" s="5">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A283" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E283" s="5" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G283" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="H283" s="5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I283" s="5" t="s">
+        <v>2204</v>
+      </c>
+      <c r="J283" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="K283" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A284" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E284" s="5" t="s">
+        <v>2208</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="G284" s="5" t="s">
+        <v>2210</v>
+      </c>
+      <c r="H284" s="5" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I284" s="5" t="s">
+        <v>2212</v>
+      </c>
+      <c r="J284" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="K284" s="5">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A285" s="5" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E285" s="5" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G285" s="5" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H285" s="5" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I285" s="5" t="s">
+        <v>2220</v>
+      </c>
+      <c r="J285" s="5" t="s">
+        <v>2221</v>
+      </c>
+      <c r="K285" s="5">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A286" s="5" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E286" s="5" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>2225</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H286" s="5" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I286" s="5" t="s">
+        <v>2228</v>
+      </c>
+      <c r="J286" s="5" t="s">
+        <v>2229</v>
+      </c>
+      <c r="K286" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A287" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E287" s="5" t="s">
+        <v>2232</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>2234</v>
+      </c>
+      <c r="H287" s="5" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I287" s="5" t="s">
+        <v>2236</v>
+      </c>
+      <c r="J287" s="5" t="s">
+        <v>2237</v>
+      </c>
+      <c r="K287" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A288" s="5" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>2239</v>
+      </c>
+      <c r="E288" s="5" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>2241</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>2242</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I288" s="5" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J288" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K288" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A289" s="5" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E289" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F289" s="5" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I289" s="5" t="s">
+        <v>2252</v>
+      </c>
+      <c r="J289" s="5" t="s">
+        <v>2253</v>
+      </c>
+      <c r="K289" s="5">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A290" s="5" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E290" s="5" t="s">
+        <v>2257</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G290" s="5" t="s">
+        <v>2259</v>
+      </c>
+      <c r="H290" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I290" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J290" s="5" t="s">
+        <v>2262</v>
+      </c>
+      <c r="K290" s="5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A291" s="5" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E291" s="5" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>2266</v>
+      </c>
+      <c r="G291" s="5" t="s">
+        <v>2267</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I291" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="J291" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="K291" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A292" s="5" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E292" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G292" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I292" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="J292" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="K292" s="5">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A293" s="5" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E293" s="5" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G293" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H293" s="5" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I293" s="5" t="s">
+        <v>2286</v>
+      </c>
+      <c r="J293" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="K293" s="5">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A294" s="5" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E294" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="G294" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="H294" s="5" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I294" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J294" s="5" t="s">
+        <v>2295</v>
+      </c>
+      <c r="K294" s="5">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A295" s="5" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E295" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="G295" s="5" t="s">
+        <v>2299</v>
+      </c>
+      <c r="H295" s="5" t="s">
+        <v>2300</v>
+      </c>
+      <c r="I295" s="5" t="s">
+        <v>2301</v>
+      </c>
+      <c r="J295" s="5" t="s">
+        <v>2302</v>
+      </c>
+      <c r="K295" s="5">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A296" s="5" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E296" s="5" t="s">
+        <v>2305</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>2306</v>
+      </c>
+      <c r="G296" s="5" t="s">
+        <v>2307</v>
+      </c>
+      <c r="H296" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I296" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J296" s="5" t="s">
+        <v>2310</v>
+      </c>
+      <c r="K296" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A297" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E297" s="5" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>2314</v>
+      </c>
+      <c r="G297" s="5" t="s">
+        <v>2315</v>
+      </c>
+      <c r="H297" s="5" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I297" s="5" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J297" s="5" t="s">
+        <v>2318</v>
+      </c>
+      <c r="K297" s="5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A298" s="5" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>2320</v>
+      </c>
+      <c r="E298" s="5" t="s">
+        <v>2321</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>2322</v>
+      </c>
+      <c r="G298" s="5" t="s">
+        <v>2323</v>
+      </c>
+      <c r="H298" s="5" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I298" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J298" s="5" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K298" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A299" s="5" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G299" s="5" t="s">
+        <v>2330</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I299" s="5" t="s">
+        <v>2332</v>
+      </c>
+      <c r="J299" s="5" t="s">
+        <v>2333</v>
+      </c>
+      <c r="K299" s="5">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A300" s="5" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E300" s="5" t="s">
+        <v>2336</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G300" s="5" t="s">
+        <v>2338</v>
+      </c>
+      <c r="H300" s="5" t="s">
+        <v>2339</v>
+      </c>
+      <c r="I300" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J300" s="5" t="s">
+        <v>2340</v>
+      </c>
+      <c r="K300" s="5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A301" s="5" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E301" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="G301" s="5" t="s">
+        <v>2346</v>
+      </c>
+      <c r="H301" s="5" t="s">
+        <v>2347</v>
+      </c>
+      <c r="I301" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="J301" s="5" t="s">
+        <v>2349</v>
+      </c>
+      <c r="K301" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A302" s="5" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>2351</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E302" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G302" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="H302" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="I302" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J302" s="5" t="s">
+        <v>2356</v>
+      </c>
+      <c r="K302" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A303" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="E303" s="5" t="s">
+        <v>2359</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="G303" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="H303" s="5" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I303" s="5" t="s">
+        <v>1528</v>
+      </c>
+      <c r="J303" s="5" t="s">
+        <v>2363</v>
+      </c>
+      <c r="K303" s="5">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A304" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E304" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G304" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="H304" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="I304" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="J304" s="5" t="s">
+        <v>2372</v>
+      </c>
+      <c r="K304" s="5">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A305" s="6" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F305" s="6" t="s">
+        <v>2376</v>
+      </c>
+      <c r="G305" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="H305" s="6" t="s">
+        <v>2378</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="J305" s="6" t="s">
+        <v>2380</v>
+      </c>
+      <c r="K305" s="6">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A306" s="6" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F306" s="6" t="s">
+        <v>2385</v>
+      </c>
+      <c r="G306" s="6" t="s">
+        <v>2386</v>
+      </c>
+      <c r="H306" s="6" t="s">
+        <v>2387</v>
+      </c>
+      <c r="I306" s="6" t="s">
+        <v>2388</v>
+      </c>
+      <c r="J306" s="6" t="s">
+        <v>2389</v>
+      </c>
+      <c r="K306" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A307" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>2391</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>2393</v>
+      </c>
+      <c r="G307" s="6" t="s">
+        <v>2394</v>
+      </c>
+      <c r="H307" s="6" t="s">
+        <v>2395</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>2396</v>
+      </c>
+      <c r="J307" s="6" t="s">
+        <v>2397</v>
+      </c>
+      <c r="K307" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A308" s="6" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E308" s="6" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F308" s="6" t="s">
+        <v>2402</v>
+      </c>
+      <c r="G308" s="6" t="s">
+        <v>2403</v>
+      </c>
+      <c r="H308" s="6" t="s">
+        <v>2404</v>
+      </c>
+      <c r="I308" s="6" t="s">
+        <v>2405</v>
+      </c>
+      <c r="J308" s="6" t="s">
+        <v>2406</v>
+      </c>
+      <c r="K308" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A309" s="6" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>2408</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F309" s="6" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G309" s="6" t="s">
+        <v>2411</v>
+      </c>
+      <c r="H309" s="6" t="s">
+        <v>2412</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>2413</v>
+      </c>
+      <c r="J309" s="6" t="s">
+        <v>2414</v>
+      </c>
+      <c r="K309" s="6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A310" s="6" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>2415</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F310" s="6" t="s">
+        <v>2417</v>
+      </c>
+      <c r="G310" s="6" t="s">
+        <v>2418</v>
+      </c>
+      <c r="H310" s="6" t="s">
+        <v>2419</v>
+      </c>
+      <c r="I310" s="6" t="s">
+        <v>2420</v>
+      </c>
+      <c r="J310" s="6" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K310" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A311" s="6" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F311" s="6" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G311" s="6" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H311" s="6" t="s">
+        <v>2426</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J311" s="6" t="s">
+        <v>2428</v>
+      </c>
+      <c r="K311" s="6">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A312" s="6" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E312" s="6" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F312" s="6" t="s">
+        <v>2431</v>
+      </c>
+      <c r="G312" s="6" t="s">
+        <v>2432</v>
+      </c>
+      <c r="H312" s="6" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I312" s="6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J312" s="6" t="s">
+        <v>2435</v>
+      </c>
+      <c r="K312" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A313" s="6" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E313" s="6" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F313" s="6" t="s">
+        <v>2438</v>
+      </c>
+      <c r="G313" s="6" t="s">
+        <v>2439</v>
+      </c>
+      <c r="H313" s="6" t="s">
+        <v>2440</v>
+      </c>
+      <c r="I313" s="6" t="s">
+        <v>2441</v>
+      </c>
+      <c r="J313" s="6" t="s">
+        <v>2442</v>
+      </c>
+      <c r="K313" s="6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A314" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>2443</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E314" s="6" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F314" s="6" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G314" s="6" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H314" s="6" t="s">
+        <v>2447</v>
+      </c>
+      <c r="I314" s="6" t="s">
+        <v>2448</v>
+      </c>
+      <c r="J314" s="6" t="s">
+        <v>2449</v>
+      </c>
+      <c r="K314" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A315" s="6" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>2450</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>2452</v>
+      </c>
+      <c r="E315" s="6" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F315" s="6" t="s">
+        <v>2454</v>
+      </c>
+      <c r="G315" s="6" t="s">
+        <v>2455</v>
+      </c>
+      <c r="H315" s="6" t="s">
+        <v>2456</v>
+      </c>
+      <c r="I315" s="6" t="s">
+        <v>2457</v>
+      </c>
+      <c r="J315" s="6" t="s">
+        <v>2458</v>
+      </c>
+      <c r="K315" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A316" s="6" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>2461</v>
+      </c>
+      <c r="E316" s="6" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F316" s="6" t="s">
+        <v>2463</v>
+      </c>
+      <c r="G316" s="6" t="s">
+        <v>2464</v>
+      </c>
+      <c r="H316" s="6" t="s">
+        <v>2465</v>
+      </c>
+      <c r="I316" s="6" t="s">
+        <v>2466</v>
+      </c>
+      <c r="J316" s="6" t="s">
+        <v>2467</v>
+      </c>
+      <c r="K316" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A317" s="6" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F317" s="6" t="s">
+        <v>2470</v>
+      </c>
+      <c r="G317" s="6" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H317" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>2473</v>
+      </c>
+      <c r="J317" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="K317" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A318" s="6" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>2475</v>
+      </c>
+      <c r="E318" s="6" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F318" s="6" t="s">
+        <v>2477</v>
+      </c>
+      <c r="G318" s="6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H318" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="I318" s="6" t="s">
+        <v>2480</v>
+      </c>
+      <c r="J318" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="K318" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A319" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G319" s="6" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H319" s="6" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I319" s="6" t="s">
+        <v>1923</v>
+      </c>
+      <c r="J319" s="6" t="s">
+        <v>1924</v>
+      </c>
+      <c r="K319" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A320" s="6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F320" s="6" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G320" s="6" t="s">
+        <v>2484</v>
+      </c>
+      <c r="H320" s="6" t="s">
+        <v>2485</v>
+      </c>
+      <c r="I320" s="6" t="s">
+        <v>1937</v>
+      </c>
+      <c r="J320" s="6" t="s">
+        <v>2486</v>
+      </c>
+      <c r="K320" s="6">
         <v>3000</v>
       </c>
     </row>

--- a/data/words.xlsx
+++ b/data/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14544\Desktop\TOEIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4844FC4C-E5EF-4620-AD47-EB7E4BF463DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2487AB-EBC1-41B1-BE53-9D6182CD2B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2728" uniqueCount="2423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3668" uniqueCount="2981">
   <si>
     <t>单词</t>
     <phoneticPr fontId="1"/>
@@ -35298,6 +35298,1824 @@
       <t>，关税</t>
     </r>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>auditor</t>
+  </si>
+  <si>
+    <t>guarantee</t>
+  </si>
+  <si>
+    <t>multilingual</t>
+  </si>
+  <si>
+    <t>inevitably</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>superior</t>
+  </si>
+  <si>
+    <t>aspect</t>
+  </si>
+  <si>
+    <t>maintain</t>
+  </si>
+  <si>
+    <t>harsh</t>
+  </si>
+  <si>
+    <t>critic</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>appraisal</t>
+  </si>
+  <si>
+    <t>further</t>
+  </si>
+  <si>
+    <t>unless</t>
+  </si>
+  <si>
+    <t>therefore</t>
+  </si>
+  <si>
+    <t>nevertheless</t>
+  </si>
+  <si>
+    <t>accountant</t>
+  </si>
+  <si>
+    <t>advertisement</t>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <t>publicity</t>
+  </si>
+  <si>
+    <t>alma</t>
+  </si>
+  <si>
+    <t>mater</t>
+  </si>
+  <si>
+    <t>prominent</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>prescription</t>
+  </si>
+  <si>
+    <t>occupancy</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>administration</t>
+  </si>
+  <si>
+    <t>prevent</t>
+  </si>
+  <si>
+    <t>get into</t>
+  </si>
+  <si>
+    <t>convention</t>
+  </si>
+  <si>
+    <t>objective</t>
+  </si>
+  <si>
+    <t>indicator</t>
+  </si>
+  <si>
+    <t>gradually</t>
+  </si>
+  <si>
+    <t>improve</t>
+  </si>
+  <si>
+    <t>defect</t>
+  </si>
+  <si>
+    <t>urgency</t>
+  </si>
+  <si>
+    <t>alteration</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>cellular</t>
+  </si>
+  <si>
+    <t>liability</t>
+  </si>
+  <si>
+    <t>reliability</t>
+  </si>
+  <si>
+    <t>appointment</t>
+  </si>
+  <si>
+    <t>designation</t>
+  </si>
+  <si>
+    <t>reimbursable</t>
+  </si>
+  <si>
+    <t>due to</t>
+  </si>
+  <si>
+    <t>mission</t>
+  </si>
+  <si>
+    <t>insure</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>since</t>
+  </si>
+  <si>
+    <t>faded</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>habitual</t>
+  </si>
+  <si>
+    <t>recreational</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>celebrity</t>
+  </si>
+  <si>
+    <t>orangutans</t>
+  </si>
+  <si>
+    <t>fairly</t>
+  </si>
+  <si>
+    <t>granted</t>
+  </si>
+  <si>
+    <t>grant</t>
+  </si>
+  <si>
+    <t>entrepreneur</t>
+  </si>
+  <si>
+    <t>eager</t>
+  </si>
+  <si>
+    <t>controversial</t>
+  </si>
+  <si>
+    <t>reversible</t>
+  </si>
+  <si>
+    <t>observable</t>
+  </si>
+  <si>
+    <t>distinguish</t>
+  </si>
+  <si>
+    <t>cosmetic</t>
+  </si>
+  <si>
+    <t>container</t>
+  </si>
+  <si>
+    <t>preferable</t>
+  </si>
+  <si>
+    <t>prefer</t>
+  </si>
+  <si>
+    <t>commuting</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>means</t>
+  </si>
+  <si>
+    <t>restructuring</t>
+  </si>
+  <si>
+    <t>remind</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>drill</t>
+  </si>
+  <si>
+    <t>convey</t>
+  </si>
+  <si>
+    <t>transcribe</t>
+  </si>
+  <si>
+    <t>deposit</t>
+  </si>
+  <si>
+    <t>shrink</t>
+  </si>
+  <si>
+    <t>minimize</t>
+  </si>
+  <si>
+    <t>deduct</t>
+  </si>
+  <si>
+    <t>subtract</t>
+  </si>
+  <si>
+    <t>dedicate</t>
+  </si>
+  <si>
+    <t>attribute</t>
+  </si>
+  <si>
+    <t>afford</t>
+  </si>
+  <si>
+    <t>contribute</t>
+  </si>
+  <si>
+    <t>attitude</t>
+  </si>
+  <si>
+    <t>effectuate</t>
+  </si>
+  <si>
+    <t>inflict</t>
+  </si>
+  <si>
+    <t>failure</t>
+  </si>
+  <si>
+    <t>affiliate</t>
+  </si>
+  <si>
+    <t>declare</t>
+  </si>
+  <si>
+    <t>inform</t>
+  </si>
+  <si>
+    <t>decrease</t>
+  </si>
+  <si>
+    <t>diligently</t>
+  </si>
+  <si>
+    <t>voluntarily</t>
+  </si>
+  <si>
+    <t>asset</t>
+  </si>
+  <si>
+    <t>drastically</t>
+  </si>
+  <si>
+    <t>hardly</t>
+  </si>
+  <si>
+    <t>merge</t>
+  </si>
+  <si>
+    <t>eventually</t>
+  </si>
+  <si>
+    <t>unanimously</t>
+  </si>
+  <si>
+    <t>bilaterally</t>
+  </si>
+  <si>
+    <t>separate</t>
+  </si>
+  <si>
+    <t>separately</t>
+  </si>
+  <si>
+    <t>subsidy</t>
+  </si>
+  <si>
+    <t>respectably</t>
+  </si>
+  <si>
+    <t>respectively</t>
+  </si>
+  <si>
+    <t>respectfully</t>
+  </si>
+  <si>
+    <t>thoroughly</t>
+  </si>
+  <si>
+    <t>triple</t>
+  </si>
+  <si>
+    <t>sporadically</t>
+  </si>
+  <si>
+    <t>actually</t>
+  </si>
+  <si>
+    <t>accurately</t>
+  </si>
+  <si>
+    <t>unilaterally</t>
+  </si>
+  <si>
+    <t>airfare</t>
+  </si>
+  <si>
+    <t>shallow</t>
+  </si>
+  <si>
+    <t>shallowly</t>
+  </si>
+  <si>
+    <t>valid</t>
+  </si>
+  <si>
+    <t>validate</t>
+  </si>
+  <si>
+    <t>slimly</t>
+  </si>
+  <si>
+    <t>scratch</t>
+  </si>
+  <si>
+    <t>passionately</t>
+  </si>
+  <si>
+    <t>practically</t>
+  </si>
+  <si>
+    <t>apparently</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>occasionally</t>
+  </si>
+  <si>
+    <t>need to do</t>
+  </si>
+  <si>
+    <t>BrE /nid/ /tu/ /du/; AmE /nid/ /tu/ /du/</t>
+  </si>
+  <si>
+    <t>需要做…（强调动作）</t>
+  </si>
+  <si>
+    <t>We need to do more research.
+A: What next? B: We need to do a quick check.</t>
+  </si>
+  <si>
+    <t>need to do sth; need to + V</t>
+  </si>
+  <si>
+    <t>need doing</t>
+  </si>
+  <si>
+    <t>BrE /nid/ /duɪŋ/; AmE /nid/ /duɪŋ/</t>
+  </si>
+  <si>
+    <t>需要被…（= need to be done）</t>
+  </si>
+  <si>
+    <t>The car needs repairing.
+A: Is the report ready? B: It still needs editing.</t>
+  </si>
+  <si>
+    <t>need doing; need + V-ing</t>
+  </si>
+  <si>
+    <t>形容词：性质/特征（需结合语境）</t>
+  </si>
+  <si>
+    <t>词根 + -ive（形容词后缀）</t>
+  </si>
+  <si>
+    <t>comparative more ...; superlative most ...</t>
+  </si>
+  <si>
+    <t>常用表达（需结合语境）</t>
+  </si>
+  <si>
+    <t>动词：执行/进行（需结合语境）</t>
+  </si>
+  <si>
+    <t>be considerate of</t>
+  </si>
+  <si>
+    <t>BrE /bi/ /kʌnsɪdɝʌt/ /ʌv/; AmE /bi/ /kʌnsɪdɝʌt/ /ʌv/</t>
+  </si>
+  <si>
+    <t>体谅…；为…着想</t>
+  </si>
+  <si>
+    <t>Please be considerate of your neighbors.
+A: Loud music? B: Be considerate of others.</t>
+  </si>
+  <si>
+    <t>be considerate of sb; considerate of others</t>
+  </si>
+  <si>
+    <t>change to</t>
+  </si>
+  <si>
+    <t>BrE /tʃeɪndʒ/ /tu/; AmE /tʃeɪndʒ/ /tu/</t>
+  </si>
+  <si>
+    <t>改成；转换为</t>
+  </si>
+  <si>
+    <t>Please change to a different seat.
+A: Same plan? B: No, we changed to Plan B.</t>
+  </si>
+  <si>
+    <t>change to + n.; change A to B</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>BrE /beɪsʌs/; AmE /beɪsʌs/</t>
+  </si>
+  <si>
+    <t>名词：概念/事物（需结合语境）</t>
+  </si>
+  <si>
+    <t>We discussed basis in the meeting.
+A: Any update? B: We will review basis tomorrow.</t>
+  </si>
+  <si>
+    <t>plural basises</t>
+  </si>
+  <si>
+    <t>BrE /ɔdɪtɝ/; AmE /ɔdɪtɝ/</t>
+  </si>
+  <si>
+    <t>We discussed auditor in the meeting.
+A: Any update? B: We will review auditor tomorrow.</t>
+  </si>
+  <si>
+    <t>plural auditors</t>
+  </si>
+  <si>
+    <t>BrE /ɡɛrʌnti/; AmE /ɡɛrʌnti/</t>
+  </si>
+  <si>
+    <t>We discussed guarantee in the meeting.
+A: Any update? B: We will review guarantee tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd guarantees; past guaranteed; pp guaranteed; ing guaranteing</t>
+  </si>
+  <si>
+    <t>BrE /mʌltilɪŋwʌl/; AmE /mʌltilɪŋwʌl/</t>
+  </si>
+  <si>
+    <t>We discussed multilingual in the meeting.
+A: Any update? B: We will review multilingual tomorrow.</t>
+  </si>
+  <si>
+    <t>词根 + -al（形容词/名词后缀）</t>
+  </si>
+  <si>
+    <t>plural multilinguals</t>
+  </si>
+  <si>
+    <t>BrE /ɪnɛvʌtʌbli/; AmE /ɪnɛvʌtʌbli/</t>
+  </si>
+  <si>
+    <t>以…方式；…地（副词）</t>
+  </si>
+  <si>
+    <t>We discussed inevitably in the meeting.
+A: Any update? B: We will review inevitably tomorrow.</t>
+  </si>
+  <si>
+    <t>词根 + -ly（副词后缀）</t>
+  </si>
+  <si>
+    <t>BrE /kælkjʌleɪt/; AmE /kælkjʌleɪt/</t>
+  </si>
+  <si>
+    <t>We discussed calculate in the meeting.
+A: Any update? B: We will review calculate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd calculates; past calculated; pp calculated; ing calculating</t>
+  </si>
+  <si>
+    <t>BrE /supɪriɝ/; AmE /supɪriɝ/</t>
+  </si>
+  <si>
+    <t>We discussed superior in the meeting.
+A: Any update? B: We will review superior tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /æspɛkt/; AmE /æspɛkt/</t>
+  </si>
+  <si>
+    <t>We discussed aspect in the meeting.
+A: Any update? B: We will review aspect tomorrow.</t>
+  </si>
+  <si>
+    <t>plural aspects</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>BrE /ɝbʌn/; AmE /ɝbʌn/</t>
+  </si>
+  <si>
+    <t>We discussed urban in the meeting.
+A: Any update? B: We will review urban tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /meɪnteɪn/; AmE /meɪnteɪn/</t>
+  </si>
+  <si>
+    <t>We discussed maintain in the meeting.
+A: Any update? B: We will review maintain tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd maintains; past maintained; pp maintained; ing maintaining</t>
+  </si>
+  <si>
+    <t>BrE /hɑrʃ/; AmE /hɑrʃ/</t>
+  </si>
+  <si>
+    <t>We discussed harsh in the meeting.
+A: Any update? B: We will review harsh tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /krɪtɪk/; AmE /krɪtɪk/</t>
+  </si>
+  <si>
+    <t>We discussed critic in the meeting.
+A: Any update? B: We will review critic tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /sʌbmɪt/; AmE /sʌbmɪt/</t>
+  </si>
+  <si>
+    <t>We discussed submit in the meeting.
+A: Any update? B: We will review submit tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd submits; past submitted; pp submitted; ing submitting</t>
+  </si>
+  <si>
+    <t>BrE /ʌpreɪzʌl/; AmE /ʌpreɪzʌl/</t>
+  </si>
+  <si>
+    <t>We discussed appraisal in the meeting.
+A: Any update? B: We will review appraisal tomorrow.</t>
+  </si>
+  <si>
+    <t>plural appraisals</t>
+  </si>
+  <si>
+    <t>BrE /fɝðɝ/; AmE /fɝðɝ/</t>
+  </si>
+  <si>
+    <t>We discussed further in the meeting.
+A: Any update? B: We will review further tomorrow.</t>
+  </si>
+  <si>
+    <t>re-（再/重新）+ 词根</t>
+  </si>
+  <si>
+    <t>BrE /ʌnlɛs/; AmE /ʌnlɛs/</t>
+  </si>
+  <si>
+    <t>除非；如果不</t>
+  </si>
+  <si>
+    <t>Don’t call me unless it’s urgent.
+A: Can I leave early? B: Not unless you finish.</t>
+  </si>
+  <si>
+    <t>unless + clause; unless otherwise stated</t>
+  </si>
+  <si>
+    <t>un-（否定）+ 词根</t>
+  </si>
+  <si>
+    <t>BrE /ðɛrfɔr/; AmE /ðɛrfɔr/</t>
+  </si>
+  <si>
+    <t>因此；所以（正式）</t>
+  </si>
+  <si>
+    <t>The data is incomplete; therefore, the result is uncertain.
+A: So what? B: Therefore we should rerun it.</t>
+  </si>
+  <si>
+    <t>and therefore; therefore + clause</t>
+  </si>
+  <si>
+    <t>BrE /nɛvɝðʌlɛs/; AmE /nɛvɝðʌlɛs/</t>
+  </si>
+  <si>
+    <t>然而；尽管如此（正式）</t>
+  </si>
+  <si>
+    <t>It was raining; nevertheless, we went out.
+A: Any risks? B: Nevertheless, we’ll proceed.</t>
+  </si>
+  <si>
+    <t>nevertheless, ...; nevertheless + clause</t>
+  </si>
+  <si>
+    <t>BrE /ʌkaʊntʌnt/; AmE /ʌkaʊntʌnt/</t>
+  </si>
+  <si>
+    <t>We discussed accountant in the meeting.
+A: Any update? B: We will review accountant tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ædvɝtʌzmʌnt/; AmE /ædvɝtʌzmʌnt/</t>
+  </si>
+  <si>
+    <t>We discussed advertisement in the meeting.
+A: Any update? B: We will review advertisement tomorrow.</t>
+  </si>
+  <si>
+    <t>词根 + -ment（名词后缀：结果/状态）</t>
+  </si>
+  <si>
+    <t>plural advertisements</t>
+  </si>
+  <si>
+    <t>advertise（做广告）；advertising（广告业）；publicity（宣传）</t>
+  </si>
+  <si>
+    <t>BrE /wɪðɪn/; AmE /wɪðɪn/</t>
+  </si>
+  <si>
+    <t>在…之内；不超过</t>
+  </si>
+  <si>
+    <t>Please reply within two days.
+A: How long? B: Within a week.</t>
+  </si>
+  <si>
+    <t>within + time/area; within reach; within limits</t>
+  </si>
+  <si>
+    <t>BrE /pʌblɪsʌti/; AmE /pʌblɪsʌti/</t>
+  </si>
+  <si>
+    <t>We discussed publicity in the meeting.
+A: Any update? B: We will review publicity tomorrow.</t>
+  </si>
+  <si>
+    <t>词根 + -ity（名词后缀：性质/状态）</t>
+  </si>
+  <si>
+    <t>plural publicities</t>
+  </si>
+  <si>
+    <t>BrE /ɑlmʌ/; AmE /ɑlmʌ/</t>
+  </si>
+  <si>
+    <t>We discussed alma in the meeting.
+A: Any update? B: We will review alma tomorrow.</t>
+  </si>
+  <si>
+    <t>plural almas</t>
+  </si>
+  <si>
+    <t>BrE /mɑtɝ/; AmE /mɑtɝ/</t>
+  </si>
+  <si>
+    <t>We discussed mater in the meeting.
+A: Any update? B: We will review mater tomorrow.</t>
+  </si>
+  <si>
+    <t>plural maters</t>
+  </si>
+  <si>
+    <t>BrE /prɑmʌnʌnt/; AmE /prɑmʌnʌnt/</t>
+  </si>
+  <si>
+    <t>We discussed prominent in the meeting.
+A: Any update? B: We will review prominent tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /kænsɝ/; AmE /kænsɝ/</t>
+  </si>
+  <si>
+    <t>We discussed cancer in the meeting.
+A: Any update? B: We will review cancer tomorrow.</t>
+  </si>
+  <si>
+    <t>plural cancers</t>
+  </si>
+  <si>
+    <t>BrE /prʌskrɪpʃʌn/; AmE /prʌskrɪpʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed prescription in the meeting.
+A: Any update? B: We will review prescription tomorrow.</t>
+  </si>
+  <si>
+    <t>词根 + -tion/-sion（名词后缀：过程/结果）</t>
+  </si>
+  <si>
+    <t>plural prescriptions</t>
+  </si>
+  <si>
+    <t>BrE /ɑkjʌpʌnsi/; AmE /ɑkjʌpʌnsi/</t>
+  </si>
+  <si>
+    <t>We discussed occupancy in the meeting.
+A: Any update? B: We will review occupancy tomorrow.</t>
+  </si>
+  <si>
+    <t>plural occupancies</t>
+  </si>
+  <si>
+    <t>BrE /kɝʌnt/; AmE /kɝʌnt/</t>
+  </si>
+  <si>
+    <t>We discussed current in the meeting.
+A: Any update? B: We will review current tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ædmɪnɪstreɪʃʌn/; AmE /ædmɪnɪstreɪʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed administration in the meeting.
+A: Any update? B: We will review administration tomorrow.</t>
+  </si>
+  <si>
+    <t>plural administrations</t>
+  </si>
+  <si>
+    <t>BrE /prɪvɛnt/; AmE /prɪvɛnt/</t>
+  </si>
+  <si>
+    <t>We discussed prevent in the meeting.
+A: Any update? B: We will review prevent tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ɡɛt/ /ɪntu/; AmE /ɡɛt/ /ɪntu/</t>
+  </si>
+  <si>
+    <t>进入；开始从事；陷入</t>
+  </si>
+  <si>
+    <t>He got into trouble at school.
+A: New hobby? B: I got into photography.</t>
+  </si>
+  <si>
+    <t>get into trouble; get into a habit; get into a field</t>
+  </si>
+  <si>
+    <t>BrE /kʌnvɛnʃʌn/; AmE /kʌnvɛnʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed convention in the meeting.
+A: Any update? B: We will review convention tomorrow.</t>
+  </si>
+  <si>
+    <t>plural conventions</t>
+  </si>
+  <si>
+    <t>field trip</t>
+  </si>
+  <si>
+    <t>BrE /fild/ /trɪp/; AmE /fild/ /trɪp/</t>
+  </si>
+  <si>
+    <t>实地考察；校外参观</t>
+  </si>
+  <si>
+    <t>We went on a field trip to the museum.
+A: Class today? B: No—field trip.</t>
+  </si>
+  <si>
+    <t>go on a field trip; field trip to + place</t>
+  </si>
+  <si>
+    <t>BrE /ʌbdʒɛktɪv/; AmE /ʌbdʒɛktɪv/</t>
+  </si>
+  <si>
+    <t>We discussed objective in the meeting.
+A: Any update? B: We will review objective tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ɪndʌkeɪtɝ/; AmE /ɪndʌkeɪtɝ/</t>
+  </si>
+  <si>
+    <t>We discussed indicator in the meeting.
+A: Any update? B: We will review indicator tomorrow.</t>
+  </si>
+  <si>
+    <t>plural indicators</t>
+  </si>
+  <si>
+    <t>BrE /ɡrædʒuʌli/; AmE /ɡrædʒuʌli/</t>
+  </si>
+  <si>
+    <t>We discussed gradually in the meeting.
+A: Any update? B: We will review gradually tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ɪmpruv/; AmE /ɪmpruv/</t>
+  </si>
+  <si>
+    <t>We discussed improve in the meeting.
+A: Any update? B: We will review improve tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd improves; past improved; pp improved; ing improving</t>
+  </si>
+  <si>
+    <t>BrE /difɛkt/; AmE /difɛkt/</t>
+  </si>
+  <si>
+    <t>We discussed defect in the meeting.
+A: Any update? B: We will review defect tomorrow.</t>
+  </si>
+  <si>
+    <t>plural defects</t>
+  </si>
+  <si>
+    <t>BrE /ɝdʒʌnsi/; AmE /ɝdʒʌnsi/</t>
+  </si>
+  <si>
+    <t>We discussed urgency in the meeting.
+A: Any update? B: We will review urgency tomorrow.</t>
+  </si>
+  <si>
+    <t>plural urgencies</t>
+  </si>
+  <si>
+    <t>BrE /ɔltɝeɪʃʌn/; AmE /ɔltɝeɪʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed alteration in the meeting.
+A: Any update? B: We will review alteration tomorrow.</t>
+  </si>
+  <si>
+    <t>plural alterations</t>
+  </si>
+  <si>
+    <t>BrE /ɪfɛkt/; AmE /ɪfɛkt/</t>
+  </si>
+  <si>
+    <t>We discussed effect in the meeting.
+A: Any update? B: We will review effect tomorrow.</t>
+  </si>
+  <si>
+    <t>plural effects</t>
+  </si>
+  <si>
+    <t>BrE /sɛljʌlɝ/; AmE /sɛljʌlɝ/</t>
+  </si>
+  <si>
+    <t>We discussed cellular in the meeting.
+A: Any update? B: We will review cellular tomorrow.</t>
+  </si>
+  <si>
+    <t>plural cellulars</t>
+  </si>
+  <si>
+    <t>BrE /laɪʌbɪlɪti/; AmE /laɪʌbɪlɪti/</t>
+  </si>
+  <si>
+    <t>We discussed liability in the meeting.
+A: Any update? B: We will review liability tomorrow.</t>
+  </si>
+  <si>
+    <t>plural liabilities</t>
+  </si>
+  <si>
+    <t>liable（有责任的）；reliability（可靠性，概念不同）</t>
+  </si>
+  <si>
+    <t>BrE /rilaɪʌbɪlʌti/; AmE /rilaɪʌbɪlʌti/</t>
+  </si>
+  <si>
+    <t>We discussed reliability in the meeting.
+A: Any update? B: We will review reliability tomorrow.</t>
+  </si>
+  <si>
+    <t>plural reliabilities</t>
+  </si>
+  <si>
+    <t>reliable（可靠的）；reliably（可靠地）；liability（责任）</t>
+  </si>
+  <si>
+    <t>BrE /ʌpɔɪntmʌnt/; AmE /ʌpɔɪntmʌnt/</t>
+  </si>
+  <si>
+    <t>We discussed appointment in the meeting.
+A: Any update? B: We will review appointment tomorrow.</t>
+  </si>
+  <si>
+    <t>plural appointments</t>
+  </si>
+  <si>
+    <t>BrE /dɛzʌɡneɪʃʌn/; AmE /dɛzʌɡneɪʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed designation in the meeting.
+A: Any update? B: We will review designation tomorrow.</t>
+  </si>
+  <si>
+    <t>plural designations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BrE ; AmE </t>
+  </si>
+  <si>
+    <t>We discussed reimbursable in the meeting.
+A: Any update? B: We will review reimbursable tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /du/ /tu/; AmE /du/ /tu/</t>
+  </si>
+  <si>
+    <t>由于；因为（正式）</t>
+  </si>
+  <si>
+    <t>The flight was delayed due to bad weather.
+A: Why late? B: Due to traffic.</t>
+  </si>
+  <si>
+    <t>due to + n./V-ing; due to the fact that（正式）</t>
+  </si>
+  <si>
+    <t>BrE /mɪʃʌn/; AmE /mɪʃʌn/</t>
+  </si>
+  <si>
+    <t>We discussed mission in the meeting.
+A: Any update? B: We will review mission tomorrow.</t>
+  </si>
+  <si>
+    <t>plural missions</t>
+  </si>
+  <si>
+    <t>BrE /ɪnʃʊr/; AmE /ɪnʃʊr/</t>
+  </si>
+  <si>
+    <t>We discussed insure in the meeting.
+A: Any update? B: We will review insure tomorrow.</t>
+  </si>
+  <si>
+    <t>plural insures</t>
+  </si>
+  <si>
+    <t>BrE /kleɪm/; AmE /kleɪm/</t>
+  </si>
+  <si>
+    <t>We discussed claim in the meeting.
+A: Any update? B: We will review claim tomorrow.</t>
+  </si>
+  <si>
+    <t>plural claims</t>
+  </si>
+  <si>
+    <t>BrE /sɪns/; AmE /sɪns/</t>
+  </si>
+  <si>
+    <t>自从；因为；既然</t>
+  </si>
+  <si>
+    <t>I’ve lived here since 2020.
+A: Why now? B: Since you ask, I’ll explain.</t>
+  </si>
+  <si>
+    <t>since + time; since + clause（因为）</t>
+  </si>
+  <si>
+    <t>BrE /feɪdʌd/; AmE /feɪdʌd/</t>
+  </si>
+  <si>
+    <t>We discussed faded in the meeting.
+A: Any update? B: We will review faded tomorrow.</t>
+  </si>
+  <si>
+    <t>plural fadeds</t>
+  </si>
+  <si>
+    <t>BrE /rɛzɪdɛnʃʌl/; AmE /rɛzɪdɛnʃʌl/</t>
+  </si>
+  <si>
+    <t>We discussed residential in the meeting.
+A: Any update? B: We will review residential tomorrow.</t>
+  </si>
+  <si>
+    <t>plural residentials</t>
+  </si>
+  <si>
+    <t>BrE /hʌbɪtʃuʌl/; AmE /hʌbɪtʃuʌl/</t>
+  </si>
+  <si>
+    <t>We discussed habitual in the meeting.
+A: Any update? B: We will review habitual tomorrow.</t>
+  </si>
+  <si>
+    <t>plural habituals</t>
+  </si>
+  <si>
+    <t>BrE /rɛkrieɪʃʌnʌl/; AmE /rɛkrieɪʃʌnʌl/</t>
+  </si>
+  <si>
+    <t>We discussed recreational in the meeting.
+A: Any update? B: We will review recreational tomorrow.</t>
+  </si>
+  <si>
+    <t>plural recreationals</t>
+  </si>
+  <si>
+    <t>BrE /kʌmɝʃʌl/; AmE /kʌmɝʃʌl/</t>
+  </si>
+  <si>
+    <t>We discussed commercial in the meeting.
+A: Any update? B: We will review commercial tomorrow.</t>
+  </si>
+  <si>
+    <t>plural commercials</t>
+  </si>
+  <si>
+    <t>BrE /sʌlɛbrɪti/; AmE /sʌlɛbrɪti/</t>
+  </si>
+  <si>
+    <t>We discussed celebrity in the meeting.
+A: Any update? B: We will review celebrity tomorrow.</t>
+  </si>
+  <si>
+    <t>plural celebrities</t>
+  </si>
+  <si>
+    <t>BrE /ɔræŋʌtænz/; AmE /ɔræŋʌtænz/</t>
+  </si>
+  <si>
+    <t>We discussed orangutans in the meeting.
+A: Any update? B: We will review orangutans tomorrow.</t>
+  </si>
+  <si>
+    <t>plural orangutanses</t>
+  </si>
+  <si>
+    <t>duplicate</t>
+  </si>
+  <si>
+    <t>BrE /duplʌkʌt/; AmE /duplʌkʌt/</t>
+  </si>
+  <si>
+    <t>We discussed duplicate in the meeting.
+A: Any update? B: We will review duplicate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd duplicates; past duplicated; pp duplicated; ing duplicating</t>
+  </si>
+  <si>
+    <t>BrE /fɛrli/; AmE /fɛrli/</t>
+  </si>
+  <si>
+    <t>We discussed fairly in the meeting.
+A: Any update? B: We will review fairly tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ɡræntʌd/; AmE /ɡræntʌd/</t>
+  </si>
+  <si>
+    <t>We discussed granted in the meeting.
+A: Any update? B: We will review granted tomorrow.</t>
+  </si>
+  <si>
+    <t>plural granteds</t>
+  </si>
+  <si>
+    <t>BrE /ɡrænt/; AmE /ɡrænt/</t>
+  </si>
+  <si>
+    <t>We discussed grant in the meeting.
+A: Any update? B: We will review grant tomorrow.</t>
+  </si>
+  <si>
+    <t>granted（已给予的）；granting（授予/给予）；grantor（授予方，法律）</t>
+  </si>
+  <si>
+    <t>BrE /ɑntrʌprʌnɝ/; AmE /ɑntrʌprʌnɝ/</t>
+  </si>
+  <si>
+    <t>We discussed entrepreneur in the meeting.
+A: Any update? B: We will review entrepreneur tomorrow.</t>
+  </si>
+  <si>
+    <t>plural entrepreneurs</t>
+  </si>
+  <si>
+    <t>BrE /iɡɝ/; AmE /iɡɝ/</t>
+  </si>
+  <si>
+    <t>We discussed eager in the meeting.
+A: Any update? B: We will review eager tomorrow.</t>
+  </si>
+  <si>
+    <t>plural eagers</t>
+  </si>
+  <si>
+    <t>BrE /kɑntrʌvɝʃʌl/; AmE /kɑntrʌvɝʃʌl/</t>
+  </si>
+  <si>
+    <t>We discussed controversial in the meeting.
+A: Any update? B: We will review controversial tomorrow.</t>
+  </si>
+  <si>
+    <t>plural controversials</t>
+  </si>
+  <si>
+    <t>词根 + -able/-ible（形容词后缀：可…的）</t>
+  </si>
+  <si>
+    <t>BrE /rɪvɝsʌbʌl/; AmE /rɪvɝsʌbʌl/</t>
+  </si>
+  <si>
+    <t>We discussed reversible in the meeting.
+A: Any update? B: We will review reversible tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ʌbzɝvʌbʌl/; AmE /ʌbzɝvʌbʌl/</t>
+  </si>
+  <si>
+    <t>We discussed observable in the meeting.
+A: Any update? B: We will review observable tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /dɪstɪŋɡwɪʃ/; AmE /dɪstɪŋɡwɪʃ/</t>
+  </si>
+  <si>
+    <t>We discussed distinguish in the meeting.
+A: Any update? B: We will review distinguish tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd distinguishes; past distinguished; pp distinguished; ing distinguishing</t>
+  </si>
+  <si>
+    <t>distinguishable</t>
+  </si>
+  <si>
+    <t>BrE /dɪstɪŋɡwɪʃʌbʌl/; AmE /dɪstɪŋɡwɪʃʌbʌl/</t>
+  </si>
+  <si>
+    <t>We discussed distinguishable in the meeting.
+A: Any update? B: We will review distinguishable tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /kɑzmɛtɪk/; AmE /kɑzmɛtɪk/</t>
+  </si>
+  <si>
+    <t>We discussed cosmetic in the meeting.
+A: Any update? B: We will review cosmetic tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /kʌnteɪnɝ/; AmE /kʌnteɪnɝ/</t>
+  </si>
+  <si>
+    <t>We discussed container in the meeting.
+A: Any update? B: We will review container tomorrow.</t>
+  </si>
+  <si>
+    <t>plural containers</t>
+  </si>
+  <si>
+    <t>BrE /prɛfɝʌbʌl/; AmE /prɛfɝʌbʌl/</t>
+  </si>
+  <si>
+    <t>We discussed preferable in the meeting.
+A: Any update? B: We will review preferable tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /prʌfɝ/; AmE /prʌfɝ/</t>
+  </si>
+  <si>
+    <t>We discussed prefer in the meeting.
+A: Any update? B: We will review prefer tomorrow.</t>
+  </si>
+  <si>
+    <t>plural prefers</t>
+  </si>
+  <si>
+    <t>BrE /kʌmjutɪŋ/; AmE /kʌmjutɪŋ/</t>
+  </si>
+  <si>
+    <t>We discussed commuting in the meeting.
+A: Any update? B: We will review commuting tomorrow.</t>
+  </si>
+  <si>
+    <t>plural commutings</t>
+  </si>
+  <si>
+    <t>commute</t>
+  </si>
+  <si>
+    <t>BrE /kʌmjut/; AmE /kʌmjut/</t>
+  </si>
+  <si>
+    <t>We discussed commute in the meeting.
+A: Any update? B: We will review commute tomorrow.</t>
+  </si>
+  <si>
+    <t>plural commutes</t>
+  </si>
+  <si>
+    <t>BrE /min/; AmE /min/</t>
+  </si>
+  <si>
+    <t>We discussed mean in the meeting.
+A: Any update? B: We will review mean tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd means; past meant; pp meant; ing meaning</t>
+  </si>
+  <si>
+    <t>BrE /minz/; AmE /minz/</t>
+  </si>
+  <si>
+    <t>We discussed means in the meeting.
+A: Any update? B: We will review means tomorrow.</t>
+  </si>
+  <si>
+    <t>plural meanses</t>
+  </si>
+  <si>
+    <t>BrE /ristrʌktʃɝɪŋ/; AmE /ristrʌktʃɝɪŋ/</t>
+  </si>
+  <si>
+    <t>We discussed restructuring in the meeting.
+A: Any update? B: We will review restructuring tomorrow.</t>
+  </si>
+  <si>
+    <t>plural restructurings</t>
+  </si>
+  <si>
+    <t>restructure</t>
+  </si>
+  <si>
+    <t>BrE /ristrʌktʃɝ/; AmE /ristrʌktʃɝ/</t>
+  </si>
+  <si>
+    <t>We discussed restructure in the meeting.
+A: Any update? B: We will review restructure tomorrow.</t>
+  </si>
+  <si>
+    <t>plural restructures</t>
+  </si>
+  <si>
+    <t>BrE /rimaɪnd/; AmE /rimaɪnd/</t>
+  </si>
+  <si>
+    <t>We discussed remind in the meeting.
+A: Any update? B: We will review remind tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd reminds; past reminded; pp reminded; ing reminding</t>
+  </si>
+  <si>
+    <t>BrE /rikɔl/; AmE /rikɔl/</t>
+  </si>
+  <si>
+    <t>We discussed recall in the meeting.
+A: Any update? B: We will review recall tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd recalls; past recalled; pp recalled; ing recalling</t>
+  </si>
+  <si>
+    <t>BrE /drɪl/; AmE /drɪl/</t>
+  </si>
+  <si>
+    <t>We discussed drill in the meeting.
+A: Any update? B: We will review drill tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd drills; past drilled; pp drilled; ing drilling</t>
+  </si>
+  <si>
+    <t>BrE /kʌnveɪ/; AmE /kʌnveɪ/</t>
+  </si>
+  <si>
+    <t>We discussed convey in the meeting.
+A: Any update? B: We will review convey tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd conveys; past conveyed; pp conveyed; ing conveying</t>
+  </si>
+  <si>
+    <t>BrE /trænskraɪb/; AmE /trænskraɪb/</t>
+  </si>
+  <si>
+    <t>We discussed transcribe in the meeting.
+A: Any update? B: We will review transcribe tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd transcribes; past transcribed; pp transcribed; ing transcribing</t>
+  </si>
+  <si>
+    <t>BrE /dʌpɑzɪt/; AmE /dʌpɑzɪt/</t>
+  </si>
+  <si>
+    <t>We discussed deposit in the meeting.
+A: Any update? B: We will review deposit tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd deposits; past deposited; pp deposited; ing depositing</t>
+  </si>
+  <si>
+    <t>BrE /ʃrɪŋk/; AmE /ʃrɪŋk/</t>
+  </si>
+  <si>
+    <t>We discussed shrink in the meeting.
+A: Any update? B: We will review shrink tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd shrinks; past shrank; pp shrunk; ing shrinking</t>
+  </si>
+  <si>
+    <t>BrE /mɪnʌmaɪz/; AmE /mɪnʌmaɪz/</t>
+  </si>
+  <si>
+    <t>We discussed minimize in the meeting.
+A: Any update? B: We will review minimize tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd minimizes; past minimized; pp minimized; ing minimizing</t>
+  </si>
+  <si>
+    <t>BrE /dɪdʌkt/; AmE /dɪdʌkt/</t>
+  </si>
+  <si>
+    <t>We discussed deduct in the meeting.
+A: Any update? B: We will review deduct tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd deducts; past deducted; pp deducted; ing deducting</t>
+  </si>
+  <si>
+    <t>BrE /sʌbtrækt/; AmE /sʌbtrækt/</t>
+  </si>
+  <si>
+    <t>We discussed subtract in the meeting.
+A: Any update? B: We will review subtract tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd subtracts; past subtracted; pp subtracted; ing subtracting</t>
+  </si>
+  <si>
+    <t>unauthorized</t>
+  </si>
+  <si>
+    <t>BrE /ʌnɔθɝaɪzd/; AmE /ʌnɔθɝaɪzd/</t>
+  </si>
+  <si>
+    <t>We discussed unauthorized in the meeting.
+A: Any update? B: We will review unauthorized tomorrow.</t>
+  </si>
+  <si>
+    <t>unpermitted</t>
+  </si>
+  <si>
+    <t>We discussed unpermitted in the meeting.
+A: Any update? B: We will review unpermitted tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /dɛdʌkeɪt/; AmE /dɛdʌkeɪt/</t>
+  </si>
+  <si>
+    <t>We discussed dedicate in the meeting.
+A: Any update? B: We will review dedicate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd dedicates; past dedicated; pp dedicated; ing dedicating</t>
+  </si>
+  <si>
+    <t>BrE /ætrʌbjut/; AmE /ætrʌbjut/</t>
+  </si>
+  <si>
+    <t>We discussed attribute in the meeting.
+A: Any update? B: We will review attribute tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd attributes; past attributed; pp attributed; ing attributing</t>
+  </si>
+  <si>
+    <t>BrE /ʌfɔrd/; AmE /ʌfɔrd/</t>
+  </si>
+  <si>
+    <t>We discussed afford in the meeting.
+A: Any update? B: We will review afford tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd affords; past afforded; pp afforded; ing affording</t>
+  </si>
+  <si>
+    <t>BrE /kʌntrɪbjut/; AmE /kʌntrɪbjut/</t>
+  </si>
+  <si>
+    <t>We discussed contribute in the meeting.
+A: Any update? B: We will review contribute tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd contributes; past contributed; pp contributed; ing contributing</t>
+  </si>
+  <si>
+    <t>BrE /ætʌtud/; AmE /ætʌtud/</t>
+  </si>
+  <si>
+    <t>We discussed attitude in the meeting.
+A: Any update? B: We will review attitude tomorrow.</t>
+  </si>
+  <si>
+    <t>plural attitudes</t>
+  </si>
+  <si>
+    <t>BrE /ɪfɛktʃueɪt/; AmE /ɪfɛktʃueɪt/</t>
+  </si>
+  <si>
+    <t>We discussed effectuate in the meeting.
+A: Any update? B: We will review effectuate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd effectuates; past effectuated; pp effectuated; ing effectuating</t>
+  </si>
+  <si>
+    <t>BrE /ɪnflɪkt/; AmE /ɪnflɪkt/</t>
+  </si>
+  <si>
+    <t>We discussed inflict in the meeting.
+A: Any update? B: We will review inflict tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd inflicts; past inflicted; pp inflicted; ing inflicting</t>
+  </si>
+  <si>
+    <t>BrE /feɪljɝ/; AmE /feɪljɝ/</t>
+  </si>
+  <si>
+    <t>We discussed failure in the meeting.
+A: Any update? B: We will review failure tomorrow.</t>
+  </si>
+  <si>
+    <t>plural failures</t>
+  </si>
+  <si>
+    <t>BrE /ʌfɪlieɪt/; AmE /ʌfɪlieɪt/</t>
+  </si>
+  <si>
+    <t>We discussed affiliate in the meeting.
+A: Any update? B: We will review affiliate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd affiliates; past affiliated; pp affiliated; ing affiliating</t>
+  </si>
+  <si>
+    <t>BrE /dɪklɛr/; AmE /dɪklɛr/</t>
+  </si>
+  <si>
+    <t>We discussed declare in the meeting.
+A: Any update? B: We will review declare tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd declares; past declared; pp declared; ing declaring</t>
+  </si>
+  <si>
+    <t>BrE /ɪnfɔrm/; AmE /ɪnfɔrm/</t>
+  </si>
+  <si>
+    <t>We discussed inform in the meeting.
+A: Any update? B: We will review inform tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd informs; past informed; pp informed; ing informing</t>
+  </si>
+  <si>
+    <t>BrE /dɪkris/; AmE /dɪkris/</t>
+  </si>
+  <si>
+    <t>We discussed decrease in the meeting.
+A: Any update? B: We will review decrease tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd decreases; past decreased; pp decreased; ing decreasing</t>
+  </si>
+  <si>
+    <t>BrE /dɪlʌdʒʌntli/; AmE /dɪlʌdʒʌntli/</t>
+  </si>
+  <si>
+    <t>We discussed diligently in the meeting.
+A: Any update? B: We will review diligently tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /vɑlʌntɛrʌli/; AmE /vɑlʌntɛrʌli/</t>
+  </si>
+  <si>
+    <t>We discussed voluntarily in the meeting.
+A: Any update? B: We will review voluntarily tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /æsɛt/; AmE /æsɛt/</t>
+  </si>
+  <si>
+    <t>We discussed asset in the meeting.
+A: Any update? B: We will review asset tomorrow.</t>
+  </si>
+  <si>
+    <t>plural assets</t>
+  </si>
+  <si>
+    <t>BrE /dræstɪkli/; AmE /dræstɪkli/</t>
+  </si>
+  <si>
+    <t>We discussed drastically in the meeting.
+A: Any update? B: We will review drastically tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /hɑrdli/; AmE /hɑrdli/</t>
+  </si>
+  <si>
+    <t>We discussed hardly in the meeting.
+A: Any update? B: We will review hardly tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /mɝdʒ/; AmE /mɝdʒ/</t>
+  </si>
+  <si>
+    <t>We discussed merge in the meeting.
+A: Any update? B: We will review merge tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd merges; past merged; pp merged; ing merging</t>
+  </si>
+  <si>
+    <t>BrE /ɪvɛntʃʌwʌli/; AmE /ɪvɛntʃʌwʌli/</t>
+  </si>
+  <si>
+    <t>We discussed eventually in the meeting.
+A: Any update? B: We will review eventually tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /junænʌmʌsli/; AmE /junænʌmʌsli/</t>
+  </si>
+  <si>
+    <t>We discussed unanimously in the meeting.
+A: Any update? B: We will review unanimously tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /baɪlætɝʌli/; AmE /baɪlætɝʌli/</t>
+  </si>
+  <si>
+    <t>We discussed bilaterally in the meeting.
+A: Any update? B: We will review bilaterally tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /sɛpɝeɪt/; AmE /sɛpɝeɪt/</t>
+  </si>
+  <si>
+    <t>We discussed separate in the meeting.
+A: Any update? B: We will review separate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd separates; past separated; pp separated; ing separating</t>
+  </si>
+  <si>
+    <t>BrE /sɛpɝʌtli/; AmE /sɛpɝʌtli/</t>
+  </si>
+  <si>
+    <t>We discussed separately in the meeting.
+A: Any update? B: We will review separately tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /sʌbsɪdi/; AmE /sʌbsɪdi/</t>
+  </si>
+  <si>
+    <t>We discussed subsidy in the meeting.
+A: Any update? B: We will review subsidy tomorrow.</t>
+  </si>
+  <si>
+    <t>plural subsidies</t>
+  </si>
+  <si>
+    <t>BrE /rispɛktʌbli/; AmE /rispɛktʌbli/</t>
+  </si>
+  <si>
+    <t>We discussed respectably in the meeting.
+A: Any update? B: We will review respectably tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /rɪspɛktɪvli/; AmE /rɪspɛktɪvli/</t>
+  </si>
+  <si>
+    <t>We discussed respectively in the meeting.
+A: Any update? B: We will review respectively tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /rɪspɛktfʌli/; AmE /rɪspɛktfʌli/</t>
+  </si>
+  <si>
+    <t>We discussed respectfully in the meeting.
+A: Any update? B: We will review respectfully tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /θɝoʊli/; AmE /θɝoʊli/</t>
+  </si>
+  <si>
+    <t>We discussed thoroughly in the meeting.
+A: Any update? B: We will review thoroughly tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /trɪpʌl/; AmE /trɪpʌl/</t>
+  </si>
+  <si>
+    <t>We discussed triple in the meeting.
+A: Any update? B: We will review triple tomorrow.</t>
+  </si>
+  <si>
+    <t>plural triples</t>
+  </si>
+  <si>
+    <t>BrE /spɝædɪkli/; AmE /spɝædɪkli/</t>
+  </si>
+  <si>
+    <t>We discussed sporadically in the meeting.
+A: Any update? B: We will review sporadically tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /æktʃuʌli/; AmE /æktʃuʌli/</t>
+  </si>
+  <si>
+    <t>We discussed actually in the meeting.
+A: Any update? B: We will review actually tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ækjɝʌtli/; AmE /ækjɝʌtli/</t>
+  </si>
+  <si>
+    <t>We discussed accurately in the meeting.
+A: Any update? B: We will review accurately tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /junʌlætɝʌli/; AmE /junʌlætɝʌli/</t>
+  </si>
+  <si>
+    <t>We discussed unilaterally in the meeting.
+A: Any update? B: We will review unilaterally tomorrow.</t>
+  </si>
+  <si>
+    <t>specifically</t>
+  </si>
+  <si>
+    <t>BrE /spʌsɪfɪkli/; AmE /spʌsɪfɪkli/</t>
+  </si>
+  <si>
+    <t>We discussed specifically in the meeting.
+A: Any update? B: We will review specifically tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ɛrfɛr/; AmE /ɛrfɛr/</t>
+  </si>
+  <si>
+    <t>We discussed airfare in the meeting.
+A: Any update? B: We will review airfare tomorrow.</t>
+  </si>
+  <si>
+    <t>plural airfares</t>
+  </si>
+  <si>
+    <t>BrE /ʃæloʊ/; AmE /ʃæloʊ/</t>
+  </si>
+  <si>
+    <t>We discussed shallow in the meeting.
+A: Any update? B: We will review shallow tomorrow.</t>
+  </si>
+  <si>
+    <t>We discussed shallowly in the meeting.
+A: Any update? B: We will review shallowly tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /vælɪd/; AmE /vælɪd/</t>
+  </si>
+  <si>
+    <t>We discussed valid in the meeting.
+A: Any update? B: We will review valid tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /vælʌdeɪt/; AmE /vælʌdeɪt/</t>
+  </si>
+  <si>
+    <t>We discussed validate in the meeting.
+A: Any update? B: We will review validate tomorrow.</t>
+  </si>
+  <si>
+    <t>3rd validates; past validated; pp validated; ing validating</t>
+  </si>
+  <si>
+    <t>valid（有效的）；validation（验证）；invalid（无效的）</t>
+  </si>
+  <si>
+    <t>We discussed slimly in the meeting.
+A: Any update? B: We will review slimly tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /skrætʃ/; AmE /skrætʃ/</t>
+  </si>
+  <si>
+    <t>We discussed scratch in the meeting.
+A: Any update? B: We will review scratch tomorrow.</t>
+  </si>
+  <si>
+    <t>plural scratches</t>
+  </si>
+  <si>
+    <t>BrE /pæʃʌnʌtli/; AmE /pæʃʌnʌtli/</t>
+  </si>
+  <si>
+    <t>We discussed passionately in the meeting.
+A: Any update? B: We will review passionately tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /præktɪkli/; AmE /præktɪkli/</t>
+  </si>
+  <si>
+    <t>We discussed practically in the meeting.
+A: Any update? B: We will review practically tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /ʌpɛrʌntli/; AmE /ʌpɛrʌntli/</t>
+  </si>
+  <si>
+    <t>We discussed apparently in the meeting.
+A: Any update? B: We will review apparently tomorrow.</t>
+  </si>
+  <si>
+    <t>BrE /dʒɛnɝʌl/; AmE /dʒɛnɝʌl/</t>
+  </si>
+  <si>
+    <t>We discussed general in the meeting.
+A: Any update? B: We will review general tomorrow.</t>
+  </si>
+  <si>
+    <t>plural generals</t>
+  </si>
+  <si>
+    <t>affair</t>
+  </si>
+  <si>
+    <t>BrE /ʌfɛr/; AmE /ʌfɛr/</t>
+  </si>
+  <si>
+    <t>We discussed affair in the meeting.
+A: Any update? B: We will review affair tomorrow.</t>
+  </si>
+  <si>
+    <t>plural affairs</t>
+  </si>
+  <si>
+    <t>BrE /ʌkeɪʒʌnʌli/; AmE /ʌkeɪʒʌnʌli/</t>
+  </si>
+  <si>
+    <t>We discussed occasionally in the meeting.
+A: Any update? B: We will review occasionally tomorrow.</t>
   </si>
 </sst>
 </file>
@@ -35378,7 +37196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -35392,6 +37210,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -35672,7 +37491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J303"/>
+  <dimension ref="A1:J447"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.09765625" bestFit="1" customWidth="1"/>
@@ -45383,6 +47202,3902 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A304" s="7" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>2554</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G304" s="7"/>
+      <c r="H304" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I304" s="7"/>
+      <c r="J304" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A305" s="7" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>2561</v>
+      </c>
+      <c r="G305" s="7"/>
+      <c r="H305" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I305" s="7"/>
+      <c r="J305" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A306" s="7" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>2570</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>2571</v>
+      </c>
+      <c r="G306" s="7"/>
+      <c r="H306" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I306" s="7"/>
+      <c r="J306" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A307" s="7" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>2576</v>
+      </c>
+      <c r="G307" s="7"/>
+      <c r="H307" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I307" s="7"/>
+      <c r="J307" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A308" s="7" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F308" s="7"/>
+      <c r="G308" s="7"/>
+      <c r="H308" s="7" t="s">
+        <v>2581</v>
+      </c>
+      <c r="I308" s="7"/>
+      <c r="J308" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A309" s="7" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E309" s="7" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F309" s="7"/>
+      <c r="G309" s="7"/>
+      <c r="H309" s="7" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I309" s="7"/>
+      <c r="J309" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A310" s="7" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>2586</v>
+      </c>
+      <c r="F310" s="7"/>
+      <c r="G310" s="7"/>
+      <c r="H310" s="7" t="s">
+        <v>2587</v>
+      </c>
+      <c r="I310" s="7"/>
+      <c r="J310" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A311" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F311" s="7"/>
+      <c r="G311" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>2591</v>
+      </c>
+      <c r="I311" s="7"/>
+      <c r="J311" s="7">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A312" s="7" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>2592</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F312" s="7"/>
+      <c r="G312" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I312" s="7"/>
+      <c r="J312" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A313" s="7" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F313" s="7"/>
+      <c r="G313" s="7"/>
+      <c r="H313" s="7" t="s">
+        <v>2598</v>
+      </c>
+      <c r="I313" s="7"/>
+      <c r="J313" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A314" s="7" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F314" s="7"/>
+      <c r="G314" s="7"/>
+      <c r="H314" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I314" s="7"/>
+      <c r="J314" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A315" s="7" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F315" s="7"/>
+      <c r="G315" s="7"/>
+      <c r="H315" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="I315" s="7"/>
+      <c r="J315" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A316" s="7" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F316" s="7"/>
+      <c r="G316" s="7"/>
+      <c r="H316" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I316" s="7"/>
+      <c r="J316" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A317" s="7" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F317" s="7"/>
+      <c r="G317" s="7"/>
+      <c r="H317" s="7" t="s">
+        <v>2609</v>
+      </c>
+      <c r="I317" s="7"/>
+      <c r="J317" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A318" s="7" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F318" s="7"/>
+      <c r="G318" s="7"/>
+      <c r="H318" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I318" s="7"/>
+      <c r="J318" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A319" s="7" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F319" s="7"/>
+      <c r="G319" s="7"/>
+      <c r="H319" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I319" s="7"/>
+      <c r="J319" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A320" s="7" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F320" s="7"/>
+      <c r="G320" s="7"/>
+      <c r="H320" s="7" t="s">
+        <v>2616</v>
+      </c>
+      <c r="I320" s="7"/>
+      <c r="J320" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A321" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>2617</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F321" s="7"/>
+      <c r="G321" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="I321" s="7"/>
+      <c r="J321" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A322" s="7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C322" s="7" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D322" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F322" s="7"/>
+      <c r="G322" s="7"/>
+      <c r="H322" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I322" s="7"/>
+      <c r="J322" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A323" s="7" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>2624</v>
+      </c>
+      <c r="E323" s="7" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>2626</v>
+      </c>
+      <c r="G323" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I323" s="7"/>
+      <c r="J323" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A324" s="7" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>2629</v>
+      </c>
+      <c r="E324" s="7" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G324" s="7"/>
+      <c r="H324" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I324" s="7"/>
+      <c r="J324" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A325" s="7" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G325" s="7"/>
+      <c r="H325" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I325" s="7"/>
+      <c r="J325" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A326" s="7" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F326" s="7"/>
+      <c r="G326" s="7"/>
+      <c r="H326" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I326" s="7"/>
+      <c r="J326" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A327" s="7" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E327" s="7" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F327" s="7"/>
+      <c r="G327" s="7" t="s">
+        <v>2640</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>2641</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>2642</v>
+      </c>
+      <c r="J327" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A328" s="7" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>2645</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>2646</v>
+      </c>
+      <c r="G328" s="7"/>
+      <c r="H328" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I328" s="7"/>
+      <c r="J328" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A329" s="7" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D329" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F329" s="7"/>
+      <c r="G329" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H329" s="7" t="s">
+        <v>2650</v>
+      </c>
+      <c r="I329" s="7"/>
+      <c r="J329" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A330" s="7" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D330" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F330" s="7"/>
+      <c r="G330" s="7"/>
+      <c r="H330" s="7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="I330" s="7"/>
+      <c r="J330" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A331" s="7" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>2654</v>
+      </c>
+      <c r="D331" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F331" s="7"/>
+      <c r="G331" s="7"/>
+      <c r="H331" s="7" t="s">
+        <v>2656</v>
+      </c>
+      <c r="I331" s="7"/>
+      <c r="J331" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A332" s="7" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D332" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F332" s="7"/>
+      <c r="G332" s="7"/>
+      <c r="H332" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I332" s="7"/>
+      <c r="J332" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A333" s="7" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C333" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>2660</v>
+      </c>
+      <c r="F333" s="7"/>
+      <c r="G333" s="7"/>
+      <c r="H333" s="7" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I333" s="7"/>
+      <c r="J333" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A334" s="7" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F334" s="7"/>
+      <c r="G334" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>2665</v>
+      </c>
+      <c r="I334" s="7"/>
+      <c r="J334" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A335" s="7" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F335" s="7"/>
+      <c r="G335" s="7"/>
+      <c r="H335" s="7" t="s">
+        <v>2668</v>
+      </c>
+      <c r="I335" s="7"/>
+      <c r="J335" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A336" s="7" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>2670</v>
+      </c>
+      <c r="F336" s="7"/>
+      <c r="G336" s="7"/>
+      <c r="H336" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I336" s="7"/>
+      <c r="J336" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A337" s="7" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C337" s="7" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D337" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E337" s="7" t="s">
+        <v>2672</v>
+      </c>
+      <c r="F337" s="7"/>
+      <c r="G337" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H337" s="7" t="s">
+        <v>2673</v>
+      </c>
+      <c r="I337" s="7"/>
+      <c r="J337" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A338" s="7" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C338" s="7" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D338" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>2675</v>
+      </c>
+      <c r="F338" s="7"/>
+      <c r="G338" s="7"/>
+      <c r="H338" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I338" s="7"/>
+      <c r="J338" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A339" s="7" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C339" s="7" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D339" s="7" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>2678</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="G339" s="7"/>
+      <c r="H339" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I339" s="7"/>
+      <c r="J339" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A340" s="7" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C340" s="7" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F340" s="7"/>
+      <c r="G340" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>2682</v>
+      </c>
+      <c r="I340" s="7"/>
+      <c r="J340" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A341" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D341" s="7" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>2686</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>2687</v>
+      </c>
+      <c r="G341" s="7"/>
+      <c r="H341" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I341" s="7"/>
+      <c r="J341" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A342" s="7" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F342" s="7"/>
+      <c r="G342" s="7" t="s">
+        <v>2563</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I342" s="7"/>
+      <c r="J342" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A343" s="7" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F343" s="7"/>
+      <c r="G343" s="7"/>
+      <c r="H343" s="7" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I343" s="7"/>
+      <c r="J343" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A344" s="7" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F344" s="7"/>
+      <c r="G344" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I344" s="7"/>
+      <c r="J344" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A345" s="7" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C345" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D345" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E345" s="7" t="s">
+        <v>2696</v>
+      </c>
+      <c r="F345" s="7"/>
+      <c r="G345" s="7"/>
+      <c r="H345" s="7" t="s">
+        <v>2697</v>
+      </c>
+      <c r="I345" s="7"/>
+      <c r="J345" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A346" s="7" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C346" s="7" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D346" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E346" s="7" t="s">
+        <v>2699</v>
+      </c>
+      <c r="F346" s="7"/>
+      <c r="G346" s="7"/>
+      <c r="H346" s="7" t="s">
+        <v>2700</v>
+      </c>
+      <c r="I346" s="7"/>
+      <c r="J346" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A347" s="7" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C347" s="7" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D347" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E347" s="7" t="s">
+        <v>2702</v>
+      </c>
+      <c r="F347" s="7"/>
+      <c r="G347" s="7"/>
+      <c r="H347" s="7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="I347" s="7"/>
+      <c r="J347" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A348" s="7" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C348" s="7" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D348" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E348" s="7" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F348" s="7"/>
+      <c r="G348" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>2706</v>
+      </c>
+      <c r="I348" s="7"/>
+      <c r="J348" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A349" s="7" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C349" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D349" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E349" s="7" t="s">
+        <v>2708</v>
+      </c>
+      <c r="F349" s="7"/>
+      <c r="G349" s="7"/>
+      <c r="H349" s="7" t="s">
+        <v>2709</v>
+      </c>
+      <c r="I349" s="7"/>
+      <c r="J349" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A350" s="7" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C350" s="7" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D350" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E350" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="F350" s="7"/>
+      <c r="G350" s="7"/>
+      <c r="H350" s="7" t="s">
+        <v>2712</v>
+      </c>
+      <c r="I350" s="7"/>
+      <c r="J350" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A351" s="7" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351" s="7" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D351" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E351" s="7" t="s">
+        <v>2714</v>
+      </c>
+      <c r="F351" s="7"/>
+      <c r="G351" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>2716</v>
+      </c>
+      <c r="J351" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A352" s="7" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352" s="7" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D352" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E352" s="7" t="s">
+        <v>2718</v>
+      </c>
+      <c r="F352" s="7"/>
+      <c r="G352" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>2719</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>2720</v>
+      </c>
+      <c r="J352" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A353" s="7" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353" s="7" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D353" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E353" s="7" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F353" s="7"/>
+      <c r="G353" s="7" t="s">
+        <v>2640</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I353" s="7"/>
+      <c r="J353" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A354" s="7" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C354" s="7" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D354" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>2725</v>
+      </c>
+      <c r="F354" s="7"/>
+      <c r="G354" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>2726</v>
+      </c>
+      <c r="I354" s="7"/>
+      <c r="J354" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A355" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C355" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F355" s="7"/>
+      <c r="G355" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I355" s="7"/>
+      <c r="J355" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A356" s="7" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C356" s="7" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D356" s="7" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E356" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>2732</v>
+      </c>
+      <c r="G356" s="7"/>
+      <c r="H356" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A357" s="7" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357" s="7" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D357" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E357" s="7" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F357" s="7"/>
+      <c r="G357" s="7" t="s">
+        <v>2664</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="I357" s="7"/>
+      <c r="J357" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A358" s="7" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C358" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D358" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E358" s="7" t="s">
+        <v>2737</v>
+      </c>
+      <c r="F358" s="7"/>
+      <c r="G358" s="7"/>
+      <c r="H358" s="7" t="s">
+        <v>2738</v>
+      </c>
+      <c r="I358" s="7"/>
+      <c r="J358" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A359" s="7" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D359" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E359" s="7" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F359" s="7"/>
+      <c r="G359" s="7"/>
+      <c r="H359" s="7" t="s">
+        <v>2741</v>
+      </c>
+      <c r="I359" s="7"/>
+      <c r="J359" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A360" s="7" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C360" s="7" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D360" s="7" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E360" s="7" t="s">
+        <v>2744</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>2745</v>
+      </c>
+      <c r="G360" s="7"/>
+      <c r="H360" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I360" s="7"/>
+      <c r="J360" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A361" s="7" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C361" s="7" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D361" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E361" s="7" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F361" s="7"/>
+      <c r="G361" s="7"/>
+      <c r="H361" s="7" t="s">
+        <v>2748</v>
+      </c>
+      <c r="I361" s="7"/>
+      <c r="J361" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A362" s="7" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C362" s="7" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D362" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E362" s="7" t="s">
+        <v>2750</v>
+      </c>
+      <c r="F362" s="7"/>
+      <c r="G362" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>2751</v>
+      </c>
+      <c r="I362" s="7"/>
+      <c r="J362" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A363" s="7" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C363" s="7" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D363" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>2753</v>
+      </c>
+      <c r="F363" s="7"/>
+      <c r="G363" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>2754</v>
+      </c>
+      <c r="I363" s="7"/>
+      <c r="J363" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A364" s="7" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C364" s="7" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D364" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F364" s="7"/>
+      <c r="G364" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>2757</v>
+      </c>
+      <c r="I364" s="7"/>
+      <c r="J364" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A365" s="7" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>2759</v>
+      </c>
+      <c r="F365" s="7"/>
+      <c r="G365" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>2760</v>
+      </c>
+      <c r="I365" s="7"/>
+      <c r="J365" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A366" s="7" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D366" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E366" s="7" t="s">
+        <v>2762</v>
+      </c>
+      <c r="F366" s="7"/>
+      <c r="G366" s="7" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>2763</v>
+      </c>
+      <c r="I366" s="7"/>
+      <c r="J366" s="7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A367" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D367" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E367" s="7" t="s">
+        <v>2765</v>
+      </c>
+      <c r="F367" s="7"/>
+      <c r="G367" s="7"/>
+      <c r="H367" s="7" t="s">
+        <v>2766</v>
+      </c>
+      <c r="I367" s="7"/>
+      <c r="J367" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A368" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C368" s="7" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D368" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E368" s="7" t="s">
+        <v>2769</v>
+      </c>
+      <c r="F368" s="7"/>
+      <c r="G368" s="7"/>
+      <c r="H368" s="7" t="s">
+        <v>2770</v>
+      </c>
+      <c r="I368" s="7"/>
+      <c r="J368" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A369" s="7" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C369" s="7" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D369" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>2772</v>
+      </c>
+      <c r="F369" s="7"/>
+      <c r="G369" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I369" s="7"/>
+      <c r="J369" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A370" s="7" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C370" s="7" t="s">
+        <v>2773</v>
+      </c>
+      <c r="D370" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E370" s="7" t="s">
+        <v>2774</v>
+      </c>
+      <c r="F370" s="7"/>
+      <c r="G370" s="7"/>
+      <c r="H370" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="I370" s="7"/>
+      <c r="J370" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A371" s="7" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C371" s="7" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D371" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E371" s="7" t="s">
+        <v>2777</v>
+      </c>
+      <c r="F371" s="7"/>
+      <c r="G371" s="7"/>
+      <c r="H371" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>2778</v>
+      </c>
+      <c r="J371" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A372" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C372" s="7" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E372" s="7" t="s">
+        <v>2780</v>
+      </c>
+      <c r="F372" s="7"/>
+      <c r="G372" s="7"/>
+      <c r="H372" s="7" t="s">
+        <v>2781</v>
+      </c>
+      <c r="I372" s="7"/>
+      <c r="J372" s="7">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A373" s="7" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C373" s="7" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E373" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="F373" s="7"/>
+      <c r="G373" s="7"/>
+      <c r="H373" s="7" t="s">
+        <v>2784</v>
+      </c>
+      <c r="I373" s="7"/>
+      <c r="J373" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A374" s="7" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C374" s="7" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E374" s="7" t="s">
+        <v>2786</v>
+      </c>
+      <c r="F374" s="7"/>
+      <c r="G374" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>2787</v>
+      </c>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A375" s="7" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C375" s="7" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E375" s="7" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F375" s="7"/>
+      <c r="G375" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I375" s="7"/>
+      <c r="J375" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A376" s="7" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C376" s="7" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F376" s="7"/>
+      <c r="G376" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I376" s="7"/>
+      <c r="J376" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A377" s="7" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C377" s="7" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D377" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F377" s="7"/>
+      <c r="G377" s="7"/>
+      <c r="H377" s="7" t="s">
+        <v>2795</v>
+      </c>
+      <c r="I377" s="7"/>
+      <c r="J377" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A378" s="7" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C378" s="7" t="s">
+        <v>2797</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>2798</v>
+      </c>
+      <c r="F378" s="7"/>
+      <c r="G378" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I378" s="7"/>
+      <c r="J378" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A379" s="7" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C379" s="7" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>2800</v>
+      </c>
+      <c r="F379" s="7"/>
+      <c r="G379" s="7"/>
+      <c r="H379" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I379" s="7"/>
+      <c r="J379" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A380" s="7" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C380" s="7" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>2802</v>
+      </c>
+      <c r="F380" s="7"/>
+      <c r="G380" s="7"/>
+      <c r="H380" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A381" s="7" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C381" s="7" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>2805</v>
+      </c>
+      <c r="F381" s="7"/>
+      <c r="G381" s="7" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I381" s="7"/>
+      <c r="J381" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A382" s="7" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C382" s="7" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D382" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="F382" s="7"/>
+      <c r="G382" s="7"/>
+      <c r="H382" s="7" t="s">
+        <v>2808</v>
+      </c>
+      <c r="I382" s="7"/>
+      <c r="J382" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A383" s="7" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C383" s="7" t="s">
+        <v>2809</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>2810</v>
+      </c>
+      <c r="F383" s="7"/>
+      <c r="G383" s="7"/>
+      <c r="H383" s="7" t="s">
+        <v>2811</v>
+      </c>
+      <c r="I383" s="7"/>
+      <c r="J383" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A384" s="7" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C384" s="7" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D384" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>2814</v>
+      </c>
+      <c r="F384" s="7"/>
+      <c r="G384" s="7"/>
+      <c r="H384" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="I384" s="7"/>
+      <c r="J384" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A385" s="7" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C385" s="7" t="s">
+        <v>2816</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F385" s="7"/>
+      <c r="G385" s="7"/>
+      <c r="H385" s="7" t="s">
+        <v>2818</v>
+      </c>
+      <c r="I385" s="7"/>
+      <c r="J385" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A386" s="7" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C386" s="7" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>2820</v>
+      </c>
+      <c r="F386" s="7"/>
+      <c r="G386" s="7"/>
+      <c r="H386" s="7" t="s">
+        <v>2821</v>
+      </c>
+      <c r="I386" s="7"/>
+      <c r="J386" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A387" s="7" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C387" s="7" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F387" s="7"/>
+      <c r="G387" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>2824</v>
+      </c>
+      <c r="I387" s="7"/>
+      <c r="J387" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A388" s="7" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>2826</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>2827</v>
+      </c>
+      <c r="F388" s="7"/>
+      <c r="G388" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>2828</v>
+      </c>
+      <c r="I388" s="7"/>
+      <c r="J388" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A389" s="7" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C389" s="7" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D389" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E389" s="7" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F389" s="7"/>
+      <c r="G389" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H389" s="7" t="s">
+        <v>2831</v>
+      </c>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A390" s="7" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>2833</v>
+      </c>
+      <c r="F390" s="7"/>
+      <c r="G390" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>2834</v>
+      </c>
+      <c r="I390" s="7"/>
+      <c r="J390" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A391" s="7" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>2835</v>
+      </c>
+      <c r="D391" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E391" s="7" t="s">
+        <v>2836</v>
+      </c>
+      <c r="F391" s="7"/>
+      <c r="G391" s="7"/>
+      <c r="H391" s="7" t="s">
+        <v>2837</v>
+      </c>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A392" s="7" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>2839</v>
+      </c>
+      <c r="F392" s="7"/>
+      <c r="G392" s="7"/>
+      <c r="H392" s="7" t="s">
+        <v>2840</v>
+      </c>
+      <c r="I392" s="7"/>
+      <c r="J392" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A393" s="7" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>2841</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>2842</v>
+      </c>
+      <c r="F393" s="7"/>
+      <c r="G393" s="7"/>
+      <c r="H393" s="7" t="s">
+        <v>2843</v>
+      </c>
+      <c r="I393" s="7"/>
+      <c r="J393" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A394" s="7" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>2845</v>
+      </c>
+      <c r="F394" s="7"/>
+      <c r="G394" s="7"/>
+      <c r="H394" s="7" t="s">
+        <v>2846</v>
+      </c>
+      <c r="I394" s="7"/>
+      <c r="J394" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A395" s="7" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>2847</v>
+      </c>
+      <c r="D395" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>2848</v>
+      </c>
+      <c r="F395" s="7"/>
+      <c r="G395" s="7"/>
+      <c r="H395" s="7" t="s">
+        <v>2849</v>
+      </c>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A396" s="7" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C396" s="7" t="s">
+        <v>2850</v>
+      </c>
+      <c r="D396" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>2851</v>
+      </c>
+      <c r="F396" s="7"/>
+      <c r="G396" s="7"/>
+      <c r="H396" s="7" t="s">
+        <v>2852</v>
+      </c>
+      <c r="I396" s="7"/>
+      <c r="J396" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A397" s="7" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>2854</v>
+      </c>
+      <c r="F397" s="7"/>
+      <c r="G397" s="7"/>
+      <c r="H397" s="7" t="s">
+        <v>2855</v>
+      </c>
+      <c r="I397" s="7"/>
+      <c r="J397" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A398" s="7" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C398" s="7" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D398" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E398" s="7" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F398" s="7"/>
+      <c r="G398" s="7"/>
+      <c r="H398" s="7" t="s">
+        <v>2858</v>
+      </c>
+      <c r="I398" s="7"/>
+      <c r="J398" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A399" s="7" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C399" s="7" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D399" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E399" s="7" t="s">
+        <v>2861</v>
+      </c>
+      <c r="F399" s="7"/>
+      <c r="G399" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H399" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I399" s="7"/>
+      <c r="J399" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A400" s="7" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C400" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D400" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>2863</v>
+      </c>
+      <c r="F400" s="7"/>
+      <c r="G400" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H400" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I400" s="7"/>
+      <c r="J400" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A401" s="7" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>2864</v>
+      </c>
+      <c r="D401" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>2865</v>
+      </c>
+      <c r="F401" s="7"/>
+      <c r="G401" s="7"/>
+      <c r="H401" s="7" t="s">
+        <v>2866</v>
+      </c>
+      <c r="I401" s="7"/>
+      <c r="J401" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A402" s="7" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C402" s="7" t="s">
+        <v>2867</v>
+      </c>
+      <c r="D402" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E402" s="7" t="s">
+        <v>2868</v>
+      </c>
+      <c r="F402" s="7"/>
+      <c r="G402" s="7"/>
+      <c r="H402" s="7" t="s">
+        <v>2869</v>
+      </c>
+      <c r="I402" s="7"/>
+      <c r="J402" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A403" s="7" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>2870</v>
+      </c>
+      <c r="D403" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E403" s="7" t="s">
+        <v>2871</v>
+      </c>
+      <c r="F403" s="7"/>
+      <c r="G403" s="7"/>
+      <c r="H403" s="7" t="s">
+        <v>2872</v>
+      </c>
+      <c r="I403" s="7"/>
+      <c r="J403" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A404" s="7" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>2873</v>
+      </c>
+      <c r="D404" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E404" s="7" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F404" s="7"/>
+      <c r="G404" s="7"/>
+      <c r="H404" s="7" t="s">
+        <v>2875</v>
+      </c>
+      <c r="I404" s="7"/>
+      <c r="J404" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A405" s="7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E405" s="7" t="s">
+        <v>2877</v>
+      </c>
+      <c r="F405" s="7"/>
+      <c r="G405" s="7"/>
+      <c r="H405" s="7" t="s">
+        <v>2878</v>
+      </c>
+      <c r="I405" s="7"/>
+      <c r="J405" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A406" s="7" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>2879</v>
+      </c>
+      <c r="D406" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E406" s="7" t="s">
+        <v>2880</v>
+      </c>
+      <c r="F406" s="7"/>
+      <c r="G406" s="7"/>
+      <c r="H406" s="7" t="s">
+        <v>2881</v>
+      </c>
+      <c r="I406" s="7"/>
+      <c r="J406" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A407" s="7" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D407" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E407" s="7" t="s">
+        <v>2883</v>
+      </c>
+      <c r="F407" s="7"/>
+      <c r="G407" s="7"/>
+      <c r="H407" s="7" t="s">
+        <v>2884</v>
+      </c>
+      <c r="I407" s="7"/>
+      <c r="J407" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A408" s="7" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E408" s="7" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F408" s="7"/>
+      <c r="G408" s="7"/>
+      <c r="H408" s="7" t="s">
+        <v>2887</v>
+      </c>
+      <c r="I408" s="7"/>
+      <c r="J408" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A409" s="7" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D409" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E409" s="7" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F409" s="7"/>
+      <c r="G409" s="7"/>
+      <c r="H409" s="7" t="s">
+        <v>2890</v>
+      </c>
+      <c r="I409" s="7"/>
+      <c r="J409" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A410" s="7" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D410" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E410" s="7" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F410" s="7"/>
+      <c r="G410" s="7"/>
+      <c r="H410" s="7" t="s">
+        <v>2893</v>
+      </c>
+      <c r="I410" s="7"/>
+      <c r="J410" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A411" s="7" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>2894</v>
+      </c>
+      <c r="D411" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E411" s="7" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F411" s="7"/>
+      <c r="G411" s="7"/>
+      <c r="H411" s="7" t="s">
+        <v>2896</v>
+      </c>
+      <c r="I411" s="7"/>
+      <c r="J411" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A412" s="7" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D412" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E412" s="7" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F412" s="7"/>
+      <c r="G412" s="7"/>
+      <c r="H412" s="7" t="s">
+        <v>2899</v>
+      </c>
+      <c r="I412" s="7"/>
+      <c r="J412" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A413" s="7" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C413" s="7" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D413" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E413" s="7" t="s">
+        <v>2901</v>
+      </c>
+      <c r="F413" s="7"/>
+      <c r="G413" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H413" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I413" s="7"/>
+      <c r="J413" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A414" s="7" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C414" s="7" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D414" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E414" s="7" t="s">
+        <v>2903</v>
+      </c>
+      <c r="F414" s="7"/>
+      <c r="G414" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H414" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I414" s="7"/>
+      <c r="J414" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A415" s="7" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C415" s="7" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D415" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E415" s="7" t="s">
+        <v>2905</v>
+      </c>
+      <c r="F415" s="7"/>
+      <c r="G415" s="7"/>
+      <c r="H415" s="7" t="s">
+        <v>2906</v>
+      </c>
+      <c r="I415" s="7"/>
+      <c r="J415" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A416" s="7" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C416" s="7" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D416" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E416" s="7" t="s">
+        <v>2908</v>
+      </c>
+      <c r="F416" s="7"/>
+      <c r="G416" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H416" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I416" s="7"/>
+      <c r="J416" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A417" s="7" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C417" s="7" t="s">
+        <v>2909</v>
+      </c>
+      <c r="D417" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E417" s="7" t="s">
+        <v>2910</v>
+      </c>
+      <c r="F417" s="7"/>
+      <c r="G417" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H417" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I417" s="7"/>
+      <c r="J417" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A418" s="7" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C418" s="7" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D418" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E418" s="7" t="s">
+        <v>2912</v>
+      </c>
+      <c r="F418" s="7"/>
+      <c r="G418" s="7"/>
+      <c r="H418" s="7" t="s">
+        <v>2913</v>
+      </c>
+      <c r="I418" s="7"/>
+      <c r="J418" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A419" s="7" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C419" s="7" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D419" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E419" s="7" t="s">
+        <v>2915</v>
+      </c>
+      <c r="F419" s="7"/>
+      <c r="G419" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I419" s="7"/>
+      <c r="J419" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A420" s="7" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C420" s="7" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D420" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E420" s="7" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F420" s="7"/>
+      <c r="G420" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H420" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I420" s="7"/>
+      <c r="J420" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A421" s="7" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C421" s="7" t="s">
+        <v>2918</v>
+      </c>
+      <c r="D421" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E421" s="7" t="s">
+        <v>2919</v>
+      </c>
+      <c r="F421" s="7"/>
+      <c r="G421" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H421" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I421" s="7"/>
+      <c r="J421" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A422" s="7" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C422" s="7" t="s">
+        <v>2920</v>
+      </c>
+      <c r="D422" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E422" s="7" t="s">
+        <v>2921</v>
+      </c>
+      <c r="F422" s="7"/>
+      <c r="G422" s="7"/>
+      <c r="H422" s="7" t="s">
+        <v>2922</v>
+      </c>
+      <c r="I422" s="7"/>
+      <c r="J422" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A423" s="7" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D423" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E423" s="7" t="s">
+        <v>2924</v>
+      </c>
+      <c r="F423" s="7"/>
+      <c r="G423" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H423" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I423" s="7"/>
+      <c r="J423" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A424" s="7" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C424" s="7" t="s">
+        <v>2925</v>
+      </c>
+      <c r="D424" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E424" s="7" t="s">
+        <v>2926</v>
+      </c>
+      <c r="F424" s="7"/>
+      <c r="G424" s="7"/>
+      <c r="H424" s="7" t="s">
+        <v>2927</v>
+      </c>
+      <c r="I424" s="7"/>
+      <c r="J424" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A425" s="7" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C425" s="7" t="s">
+        <v>2928</v>
+      </c>
+      <c r="D425" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>2929</v>
+      </c>
+      <c r="F425" s="7"/>
+      <c r="G425" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H425" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I425" s="7"/>
+      <c r="J425" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A426" s="7" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C426" s="7" t="s">
+        <v>2930</v>
+      </c>
+      <c r="D426" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E426" s="7" t="s">
+        <v>2931</v>
+      </c>
+      <c r="F426" s="7"/>
+      <c r="G426" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H426" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I426" s="7"/>
+      <c r="J426" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A427" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C427" s="7" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D427" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E427" s="7" t="s">
+        <v>2933</v>
+      </c>
+      <c r="F427" s="7"/>
+      <c r="G427" s="7" t="s">
+        <v>2622</v>
+      </c>
+      <c r="H427" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I427" s="7"/>
+      <c r="J427" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A428" s="7" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C428" s="7" t="s">
+        <v>2934</v>
+      </c>
+      <c r="D428" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E428" s="7" t="s">
+        <v>2935</v>
+      </c>
+      <c r="F428" s="7"/>
+      <c r="G428" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I428" s="7"/>
+      <c r="J428" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A429" s="7" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>2936</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E429" s="7" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F429" s="7"/>
+      <c r="G429" s="7"/>
+      <c r="H429" s="7" t="s">
+        <v>2938</v>
+      </c>
+      <c r="I429" s="7"/>
+      <c r="J429" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A430" s="7" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E430" s="7" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F430" s="7"/>
+      <c r="G430" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I430" s="7"/>
+      <c r="J430" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A431" s="7" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C431" s="7" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D431" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E431" s="7" t="s">
+        <v>2942</v>
+      </c>
+      <c r="F431" s="7"/>
+      <c r="G431" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I431" s="7"/>
+      <c r="J431" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A432" s="7" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C432" s="7" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D432" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E432" s="7" t="s">
+        <v>2944</v>
+      </c>
+      <c r="F432" s="7"/>
+      <c r="G432" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I432" s="7"/>
+      <c r="J432" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A433" s="7" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C433" s="7" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D433" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E433" s="7" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F433" s="7"/>
+      <c r="G433" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I433" s="7"/>
+      <c r="J433" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A434" s="7" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C434" s="7" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D434" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E434" s="7" t="s">
+        <v>2949</v>
+      </c>
+      <c r="F434" s="7"/>
+      <c r="G434" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I434" s="7"/>
+      <c r="J434" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A435" s="7" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C435" s="7" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D435" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E435" s="7" t="s">
+        <v>2951</v>
+      </c>
+      <c r="F435" s="7"/>
+      <c r="G435" s="7"/>
+      <c r="H435" s="7" t="s">
+        <v>2952</v>
+      </c>
+      <c r="I435" s="7"/>
+      <c r="J435" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A436" s="7" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C436" s="7" t="s">
+        <v>2953</v>
+      </c>
+      <c r="D436" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E436" s="7" t="s">
+        <v>2954</v>
+      </c>
+      <c r="F436" s="7"/>
+      <c r="G436" s="7"/>
+      <c r="H436" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I436" s="7"/>
+      <c r="J436" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A437" s="7" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C437" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D437" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E437" s="7" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F437" s="7"/>
+      <c r="G437" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H437" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I437" s="7"/>
+      <c r="J437" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A438" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C438" s="7" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D438" s="7" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E438" s="7" t="s">
+        <v>2957</v>
+      </c>
+      <c r="F438" s="7"/>
+      <c r="G438" s="7"/>
+      <c r="H438" s="7" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I438" s="7"/>
+      <c r="J438" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A439" s="7" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C439" s="7" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D439" s="7" t="s">
+        <v>2566</v>
+      </c>
+      <c r="E439" s="7" t="s">
+        <v>2959</v>
+      </c>
+      <c r="F439" s="7"/>
+      <c r="G439" s="7"/>
+      <c r="H439" s="7" t="s">
+        <v>2960</v>
+      </c>
+      <c r="I439" s="7" t="s">
+        <v>2961</v>
+      </c>
+      <c r="J439" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A440" s="7" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C440" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D440" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E440" s="7" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F440" s="7"/>
+      <c r="G440" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H440" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I440" s="7"/>
+      <c r="J440" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A441" s="7" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C441" s="7" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D441" s="7" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E441" s="7" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F441" s="7"/>
+      <c r="G441" s="7"/>
+      <c r="H441" s="7" t="s">
+        <v>2965</v>
+      </c>
+      <c r="I441" s="7"/>
+      <c r="J441" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A442" s="7" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>2966</v>
+      </c>
+      <c r="D442" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E442" s="7" t="s">
+        <v>2967</v>
+      </c>
+      <c r="F442" s="7"/>
+      <c r="G442" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H442" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I442" s="7"/>
+      <c r="J442" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A443" s="7" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C443" s="7" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D443" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E443" s="7" t="s">
+        <v>2969</v>
+      </c>
+      <c r="F443" s="7"/>
+      <c r="G443" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H443" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I443" s="7"/>
+      <c r="J443" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A444" s="7" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>2970</v>
+      </c>
+      <c r="D444" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E444" s="7" t="s">
+        <v>2971</v>
+      </c>
+      <c r="F444" s="7"/>
+      <c r="G444" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H444" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I444" s="7"/>
+      <c r="J444" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A445" s="7" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C445" s="7" t="s">
+        <v>2972</v>
+      </c>
+      <c r="D445" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E445" s="7" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F445" s="7"/>
+      <c r="G445" s="7" t="s">
+        <v>2590</v>
+      </c>
+      <c r="H445" s="7" t="s">
+        <v>2974</v>
+      </c>
+      <c r="I445" s="7"/>
+      <c r="J445" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A446" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C446" s="7" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D446" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E446" s="7" t="s">
+        <v>2977</v>
+      </c>
+      <c r="F446" s="7"/>
+      <c r="G446" s="7"/>
+      <c r="H446" s="7" t="s">
+        <v>2978</v>
+      </c>
+      <c r="I446" s="7"/>
+      <c r="J446" s="7">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A447" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D447" s="7" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E447" s="7" t="s">
+        <v>2980</v>
+      </c>
+      <c r="F447" s="7"/>
+      <c r="G447" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="H447" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I447" s="7"/>
+      <c r="J447" s="7">
+        <v>5000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
